--- a/rtss-pre1917/src/main/resources/inner-migration/1881-1895/inner-migration-1881-1895.xlsx
+++ b/rtss-pre1917/src/main/resources/inner-migration/1881-1895/inner-migration-1881-1895.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\inner-migration\1881-1895\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26107A5-1B81-4BBD-855A-77707BAA4AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C6CF48-FE16-4B38-8955-F8136E72D9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{47EC4337-547E-4887-AD04-14E4B8E0F3C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{47EC4337-547E-4887-AD04-14E4B8E0F3C0}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="1" r:id="rId1"/>
-    <sheet name="data-1" sheetId="2" r:id="rId2"/>
+    <sheet name="data-outbound" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="116">
   <si>
     <t>1862-1884</t>
   </si>
@@ -159,9 +159,6 @@
     <t>Я. Ф. Ставровский, В. В. Алексеев. «Переселение в Сибирь». Вып. XVIII. С.-Петербург, 1906. Таблица I, печатные с. 2–3.</t>
   </si>
   <si>
-    <t>data-1</t>
-  </si>
-  <si>
     <t>1893</t>
   </si>
   <si>
@@ -349,12 +346,6 @@
   </si>
   <si>
     <t>Олонецкая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Губерния </t>
-  </si>
-  <si>
-    <t>1885 -1892</t>
   </si>
   <si>
     <t>1894–1898</t>
@@ -394,6 +385,12 @@
   </si>
   <si>
     <t>Таблица I. Движение переселенцев (душ обоего пола) в Сибирь за 20 лет (1885–1904 гг.)</t>
+  </si>
+  <si>
+    <t>data-outbound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">губерния </t>
   </si>
 </sst>
 </file>
@@ -1004,9 +1001,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5100042B-733C-4FA0-B5DF-69D2DC019B96}">
   <dimension ref="A1:P110"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1026,7 +1023,7 @@
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1034,7 +1031,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -1042,7 +1039,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -1050,7 +1047,7 @@
         <v>161671</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -1058,7 +1055,7 @@
         <v>932115</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>9</v>
       </c>
@@ -1066,7 +1063,7 @@
         <v>436584</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>14</v>
       </c>
@@ -1075,7 +1072,7 @@
         <v>1830370</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>20</v>
       </c>
@@ -1095,7 +1092,7 @@
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
@@ -1103,7 +1100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>5</v>
       </c>
@@ -1111,7 +1108,7 @@
         <v>258154</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1893</v>
       </c>
@@ -1119,7 +1116,7 @@
         <v>53350</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>1894</v>
       </c>
@@ -1127,7 +1124,7 @@
         <v>55776</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1895</v>
       </c>
@@ -1135,7 +1132,7 @@
         <v>101995</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B17">
         <f>B16+1</f>
         <v>1896</v>
@@ -1144,7 +1141,7 @@
         <v>186166</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B18">
         <f t="shared" ref="B18:B24" si="0">B17+1</f>
         <v>1897</v>
@@ -1153,7 +1150,7 @@
         <v>81015</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B19">
         <f t="shared" si="0"/>
         <v>1898</v>
@@ -1162,7 +1159,7 @@
         <v>143697</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B20">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -1171,7 +1168,7 @@
         <v>162805</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B21">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -1180,7 +1177,7 @@
         <v>164639</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B22">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -1189,7 +1186,7 @@
         <v>86334</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B23">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -1198,7 +1195,7 @@
         <v>80499</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B24">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -1207,7 +1204,7 @@
         <v>83721</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>14</v>
       </c>
@@ -1216,7 +1213,7 @@
         <v>1458151</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>22</v>
       </c>
@@ -1236,7 +1233,7 @@
       <c r="O27" s="4"/>
       <c r="P27" s="4"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>1</v>
       </c>
@@ -1244,7 +1241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>1894</v>
       </c>
@@ -1252,7 +1249,7 @@
         <v>7233</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B31">
         <f>B30+1</f>
         <v>1895</v>
@@ -1261,7 +1258,7 @@
         <v>85933</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B32">
         <f t="shared" ref="B32:B39" si="1">B31+1</f>
         <v>1896</v>
@@ -1270,7 +1267,7 @@
         <v>177168</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B33">
         <f t="shared" si="1"/>
         <v>1897</v>
@@ -1279,7 +1276,7 @@
         <v>66747</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B34">
         <f t="shared" si="1"/>
         <v>1898</v>
@@ -1288,7 +1285,7 @@
         <v>144024</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B35">
         <f t="shared" si="1"/>
         <v>1899</v>
@@ -1297,7 +1294,7 @@
         <v>159747</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B36">
         <f t="shared" si="1"/>
         <v>1900</v>
@@ -1306,7 +1303,7 @@
         <v>152444</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B37">
         <f t="shared" si="1"/>
         <v>1901</v>
@@ -1315,7 +1312,7 @@
         <v>69015</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B38">
         <f t="shared" si="1"/>
         <v>1902</v>
@@ -1324,7 +1321,7 @@
         <v>64550</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B39">
         <f t="shared" si="1"/>
         <v>1903</v>
@@ -1333,7 +1330,7 @@
         <v>71139</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>16</v>
       </c>
@@ -1353,7 +1350,7 @@
       <c r="O41" s="4"/>
       <c r="P41" s="4"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
         <v>1</v>
       </c>
@@ -1361,7 +1358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>6</v>
       </c>
@@ -1369,7 +1366,7 @@
         <v>327100</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>7</v>
       </c>
@@ -1377,7 +1374,7 @@
         <v>495225</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>8</v>
       </c>
@@ -1385,7 +1382,7 @@
         <v>558071</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>14</v>
       </c>
@@ -1394,16 +1391,16 @@
         <v>1380396</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C48" s="3"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>17</v>
       </c>
       <c r="C49" s="3"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>6</v>
       </c>
@@ -1411,7 +1408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>7</v>
       </c>
@@ -1419,7 +1416,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>8</v>
       </c>
@@ -1427,7 +1424,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>27</v>
       </c>
@@ -1447,7 +1444,7 @@
       <c r="O54" s="4"/>
       <c r="P54" s="4"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>36</v>
       </c>
@@ -1467,7 +1464,7 @@
       <c r="O55" s="4"/>
       <c r="P55" s="4"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C57" s="2" t="s">
         <v>31</v>
       </c>
@@ -1478,7 +1475,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C58" s="2" t="s">
         <v>34</v>
       </c>
@@ -1487,7 +1484,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
         <v>11</v>
       </c>
@@ -1501,7 +1498,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>1896</v>
       </c>
@@ -1516,7 +1513,7 @@
         <v>159882</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>1897</v>
       </c>
@@ -1531,7 +1528,7 @@
         <v>49685</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>1898</v>
       </c>
@@ -1546,7 +1543,7 @@
         <v>143704</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B63">
         <v>1899</v>
       </c>
@@ -1561,7 +1558,7 @@
         <v>154942</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B64">
         <v>1900</v>
       </c>
@@ -1576,7 +1573,7 @@
         <v>128752</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B65">
         <v>1901</v>
       </c>
@@ -1591,7 +1588,7 @@
         <v>62932</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B66">
         <v>1902</v>
       </c>
@@ -1606,7 +1603,7 @@
         <v>64808</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>1903</v>
       </c>
@@ -1621,7 +1618,7 @@
         <v>86875</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>24</v>
       </c>
@@ -1641,7 +1638,7 @@
       <c r="O69" s="6"/>
       <c r="P69" s="6"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>25</v>
       </c>
@@ -1661,7 +1658,7 @@
       <c r="O70" s="6"/>
       <c r="P70" s="6"/>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
         <v>11</v>
       </c>
@@ -1687,7 +1684,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B73">
         <f>B74-1</f>
         <v>1881</v>
@@ -1696,7 +1693,7 @@
         <v>6492.9400850000002</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B74">
         <f>B75-1</f>
         <v>1882</v>
@@ -1705,7 +1702,7 @@
         <v>5345.4438110000001</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B75">
         <f>B76-1</f>
         <v>1883</v>
@@ -1714,7 +1711,7 @@
         <v>4174.0546619999996</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B76">
         <f>B77-1</f>
         <v>1884</v>
@@ -1723,7 +1720,7 @@
         <v>3001.3063069999998</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B77">
         <v>1885</v>
       </c>
@@ -1738,7 +1735,7 @@
         <v>22137.742243000001</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B78">
         <f>B77+1</f>
         <v>1886</v>
@@ -1754,7 +1751,7 @@
         <v>22939.139247999999</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B79">
         <f t="shared" ref="B79:B97" si="3">B78+1</f>
         <v>1887</v>
@@ -1770,7 +1767,7 @@
         <v>24614.52692</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B80">
         <f t="shared" si="3"/>
         <v>1888</v>
@@ -1786,7 +1783,7 @@
         <v>27397.393515</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B81">
         <f t="shared" si="3"/>
         <v>1889</v>
@@ -1802,7 +1799,7 @@
         <v>31425.433763000001</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B82">
         <f t="shared" si="3"/>
         <v>1890</v>
@@ -1818,7 +1815,7 @@
         <v>36879.090257000003</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B83">
         <f t="shared" si="3"/>
         <v>1891</v>
@@ -1834,7 +1831,7 @@
         <v>44008.187974</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B84">
         <f t="shared" si="3"/>
         <v>1892</v>
@@ -1850,7 +1847,7 @@
         <v>53145.628228000001</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B85">
         <f t="shared" si="3"/>
         <v>1893</v>
@@ -1866,7 +1863,7 @@
         <v>64552.857853000001</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B86">
         <f t="shared" si="3"/>
         <v>1894</v>
@@ -1884,7 +1881,7 @@
         <v>80226.789336000002</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B87">
         <f t="shared" si="3"/>
         <v>1895</v>
@@ -1902,7 +1899,7 @@
         <v>92405.860002999994</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B88">
         <f t="shared" si="3"/>
         <v>1896</v>
@@ -1930,7 +1927,7 @@
         <v>159882</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B89">
         <f t="shared" si="3"/>
         <v>1897</v>
@@ -1958,7 +1955,7 @@
         <v>49685</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B90">
         <f t="shared" si="3"/>
         <v>1898</v>
@@ -1986,7 +1983,7 @@
         <v>143704</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B91">
         <f t="shared" si="3"/>
         <v>1899</v>
@@ -2014,7 +2011,7 @@
         <v>154942</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B92">
         <f t="shared" si="3"/>
         <v>1900</v>
@@ -2042,7 +2039,7 @@
         <v>128752</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B93">
         <f t="shared" si="3"/>
         <v>1901</v>
@@ -2070,7 +2067,7 @@
         <v>62932</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B94">
         <f t="shared" si="3"/>
         <v>1902</v>
@@ -2098,7 +2095,7 @@
         <v>64808</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B95">
         <f t="shared" si="3"/>
         <v>1903</v>
@@ -2126,7 +2123,7 @@
         <v>86875</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B96">
         <f t="shared" si="3"/>
         <v>1904</v>
@@ -2135,7 +2132,7 @@
         <v>66981.996801999994</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B97">
         <f t="shared" si="3"/>
         <v>1905</v>
@@ -2144,7 +2141,7 @@
         <v>61505.744061999998</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>14</v>
       </c>
@@ -2162,7 +2159,7 @@
         <v>1380395.9999999998</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>15</v>
       </c>
@@ -2183,7 +2180,7 @@
         <v>1380395.9999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>7</v>
       </c>
@@ -2204,7 +2201,7 @@
         <v>495224.99999999994</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>8</v>
       </c>
@@ -2225,22 +2222,37 @@
         <v>558070.99999899999</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A109" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A109" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" s="26"/>
+      <c r="C109" s="26"/>
+      <c r="D109" s="26"/>
+      <c r="E109" s="26"/>
+      <c r="F109" s="26"/>
+      <c r="G109" s="26"/>
+      <c r="H109" s="26"/>
+      <c r="I109" s="26"/>
+      <c r="J109" s="26"/>
+      <c r="K109" s="26"/>
+      <c r="L109" s="26"/>
+      <c r="M109" s="26"/>
+      <c r="N109" s="26"/>
+      <c r="O109" s="26"/>
+      <c r="P109" s="26"/>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>38</v>
       </c>
@@ -2254,97 +2266,94 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF96ABE5-578E-4890-83BE-C69EB8587AC3}">
   <dimension ref="A1:AA58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.89453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.20703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.20703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.20703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.20703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.20703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.3125" customWidth="1"/>
-    <col min="10" max="10" width="10.47265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="7.20703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="6.20703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.1015625" customWidth="1"/>
-    <col min="17" max="17" width="10.47265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="10.20703125" customWidth="1"/>
-    <col min="20" max="20" width="6.20703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.47265625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.47265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="K1" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="P1" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="K1" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1" s="8" t="s">
+      <c r="S1" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="T1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="P1" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="S1" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="T1" s="8" t="s">
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="B2" s="10">
         <v>66338</v>
@@ -2426,9 +2435,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" s="13">
         <v>37276</v>
@@ -2494,7 +2503,7 @@
         <v>5024</v>
       </c>
       <c r="X3" s="25">
-        <f t="shared" ref="X3:X51" si="1">SUM(D3:H3)-I3</f>
+        <f t="shared" ref="X3:X50" si="1">SUM(D3:H3)-I3</f>
         <v>0</v>
       </c>
       <c r="Y3" s="25">
@@ -2502,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="Z3" s="25">
-        <f t="shared" ref="Z3:Z51" si="3">I3+P3-R3</f>
+        <f t="shared" ref="Z3:Z50" si="3">I3+P3-R3</f>
         <v>0</v>
       </c>
       <c r="AA3" s="25">
@@ -2510,9 +2519,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4" s="16">
         <v>5493</v>
@@ -2594,9 +2603,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="13">
         <v>6166</v>
@@ -2678,9 +2687,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6" s="16">
         <v>6335</v>
@@ -2762,9 +2771,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B7" s="13">
         <v>204</v>
@@ -2846,9 +2855,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B8" s="16">
         <v>10435</v>
@@ -2930,9 +2939,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B9" s="13">
         <v>11493</v>
@@ -3014,9 +3023,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" s="16">
         <v>9807</v>
@@ -3098,9 +3107,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="13">
         <v>21796</v>
@@ -3182,15 +3191,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D12" s="16">
         <v>46</v>
@@ -3266,18 +3275,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" s="13">
         <v>64</v>
@@ -3350,21 +3359,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="16">
         <v>428</v>
@@ -3434,18 +3443,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E15" s="13">
         <v>320</v>
@@ -3518,15 +3527,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" s="16">
         <v>49</v>
@@ -3602,15 +3611,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" s="13">
         <v>3</v>
@@ -3686,15 +3695,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18" s="16">
         <v>59</v>
@@ -3770,15 +3779,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" s="13">
         <v>26</v>
@@ -3854,15 +3863,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D20" s="16">
         <v>11</v>
@@ -3938,9 +3947,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B21" s="13">
         <v>8476</v>
@@ -4022,9 +4031,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B22" s="16">
         <v>5618</v>
@@ -4106,9 +4115,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" s="13">
         <v>4272</v>
@@ -4190,9 +4199,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B24" s="16">
         <v>9560</v>
@@ -4274,9 +4283,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B25" s="13">
         <v>5297</v>
@@ -4358,15 +4367,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D26" s="16">
         <v>28</v>
@@ -4442,15 +4451,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D27" s="13">
         <v>14</v>
@@ -4526,21 +4535,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F28" s="16">
         <v>4</v>
@@ -4570,7 +4579,7 @@
         <v>1</v>
       </c>
       <c r="O28" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P28" s="16">
         <v>67</v>
@@ -4585,7 +4594,7 @@
         <v>10</v>
       </c>
       <c r="T28" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="U28" s="16">
         <v>102</v>
@@ -4610,15 +4619,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D29" s="13">
         <v>6</v>
@@ -4694,15 +4703,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D30" s="16">
         <v>13</v>
@@ -4778,27 +4787,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F31" s="13">
         <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H31" s="13">
         <v>2</v>
@@ -4813,16 +4822,16 @@
         <v>5</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O31" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P31" s="13">
         <v>5</v>
@@ -4837,7 +4846,7 @@
         <v>0.8</v>
       </c>
       <c r="T31" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="U31" s="13">
         <v>8</v>
@@ -4862,21 +4871,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F32" s="16">
         <v>224</v>
@@ -4946,9 +4955,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B33" s="13">
         <v>450</v>
@@ -4957,7 +4966,7 @@
         <v>5</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E33" s="13">
         <v>103</v>
@@ -5030,9 +5039,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B34" s="16">
         <v>406</v>
@@ -5114,9 +5123,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B35" s="13">
         <v>60</v>
@@ -5198,18 +5207,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E36" s="16">
         <v>9</v>
@@ -5282,9 +5291,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B37" s="13">
         <v>349</v>
@@ -5366,9 +5375,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B38" s="16">
         <v>1348</v>
@@ -5450,9 +5459,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B39" s="13">
         <v>607</v>
@@ -5534,15 +5543,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D40" s="16">
         <v>21</v>
@@ -5618,9 +5627,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B41" s="13">
         <v>23696</v>
@@ -5702,9 +5711,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B42" s="16">
         <v>22672</v>
@@ -5786,18 +5795,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E43" s="13">
         <v>5</v>
@@ -5870,21 +5879,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F44" s="16">
         <v>483</v>
@@ -5929,7 +5938,7 @@
         <v>102</v>
       </c>
       <c r="T44" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="U44" s="16">
         <v>1018</v>
@@ -5954,21 +5963,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F45" s="13">
         <v>83</v>
@@ -6038,18 +6047,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E46" s="16">
         <v>202</v>
@@ -6122,15 +6131,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D47" s="13">
         <v>4</v>
@@ -6206,21 +6215,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F48" s="16">
         <v>22</v>
@@ -6290,21 +6299,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D49" s="13">
         <v>10</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F49" s="13">
         <v>147</v>
@@ -6374,30 +6383,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F50" s="16">
         <v>16</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I50" s="16">
         <v>16</v>
@@ -6415,10 +6424,10 @@
         <v>12</v>
       </c>
       <c r="N50" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O50" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P50" s="16">
         <v>210</v>
@@ -6433,7 +6442,7 @@
         <v>23</v>
       </c>
       <c r="T50" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="U50" s="16">
         <v>226</v>
@@ -6458,51 +6467,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L51" s="21">
         <v>10</v>
       </c>
       <c r="M51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P51" s="21">
         <v>10</v>
@@ -6517,7 +6526,7 @@
         <v>1</v>
       </c>
       <c r="T51" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="U51" s="21">
         <v>10</v>
@@ -6536,9 +6545,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B52" s="24">
         <v>258154</v>
@@ -6604,105 +6613,105 @@
         <v>74402</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B54" s="25">
-        <f>SUM(B2:B51)-B52</f>
+        <f t="shared" ref="B54:V54" si="4">SUM(B2:B51)-B52</f>
         <v>0</v>
       </c>
       <c r="C54" s="25">
-        <f>SUM(C2:C51)-C52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D54" s="25">
-        <f>SUM(D2:D51)-D52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E54" s="25">
-        <f>SUM(E2:E51)-E52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F54" s="25">
-        <f>SUM(F2:F51)-F52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G54" s="25">
-        <f>SUM(G2:G51)-G52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H54" s="25">
-        <f>SUM(H2:H51)-H52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I54" s="25">
-        <f>SUM(I2:I51)-I52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J54" s="25">
-        <f>SUM(J2:J51)-J52</f>
+        <f t="shared" si="4"/>
         <v>-0.39999999999417923</v>
       </c>
       <c r="K54" s="25">
-        <f>SUM(K2:K51)-K52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L54" s="25">
-        <f>SUM(L2:L51)-L52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M54" s="25">
-        <f>SUM(M2:M51)-M52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N54" s="25">
-        <f>SUM(N2:N51)-N52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O54" s="25">
-        <f>SUM(O2:O51)-O52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P54" s="25">
-        <f>SUM(P2:P51)-P52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q54" s="25">
-        <f>SUM(Q2:Q51)-Q52</f>
+        <f t="shared" si="4"/>
         <v>-1</v>
       </c>
       <c r="R54" s="25">
-        <f>SUM(R2:R51)-R52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S54" s="25">
-        <f>SUM(S2:S51)-S52</f>
+        <f t="shared" si="4"/>
         <v>0.80000000000291038</v>
       </c>
       <c r="T54" s="25">
-        <f>SUM(T2:T51)-T52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="U54" s="25">
-        <f>SUM(U2:U51)-U52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="V54" s="25">
-        <f>SUM(V2:V51)-V52</f>
+        <f t="shared" si="4"/>
         <v>-0.10000000000582077</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/rtss-pre1917/src/main/resources/inner-migration/1881-1895/inner-migration-1881-1895.xlsx
+++ b/rtss-pre1917/src/main/resources/inner-migration/1881-1895/inner-migration-1881-1895.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\inner-migration\1881-1895\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C6CF48-FE16-4B38-8955-F8136E72D9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF2C115-112A-4B6C-AF8B-70164F9E5733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{47EC4337-547E-4887-AD04-14E4B8E0F3C0}"/>
+    <workbookView xWindow="61770" yWindow="2265" windowWidth="27960" windowHeight="18360" activeTab="2" xr2:uid="{47EC4337-547E-4887-AD04-14E4B8E0F3C0}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="1" r:id="rId1"/>
-    <sheet name="data-outbound" sheetId="2" r:id="rId2"/>
+    <sheet name="1885-1904 выход доноры" sheetId="2" r:id="rId2"/>
+    <sheet name="1881-1904 выход доноры" sheetId="3" r:id="rId3"/>
+    <sheet name="1894-1896 назначение" sheetId="4" r:id="rId4"/>
+    <sheet name="оседание" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="174">
   <si>
     <t>1862-1884</t>
   </si>
@@ -387,20 +390,195 @@
     <t>Таблица I. Движение переселенцев (душ обоего пола) в Сибирь за 20 лет (1885–1904 гг.)</t>
   </si>
   <si>
-    <t>data-outbound</t>
-  </si>
-  <si>
     <t xml:space="preserve">губерния </t>
+  </si>
+  <si>
+    <t>губерния</t>
+  </si>
+  <si>
+    <t>Область войска Донского</t>
+  </si>
+  <si>
+    <t>Санкт-Петербургская</t>
+  </si>
+  <si>
+    <t>1885-1904 выход доноры</t>
+  </si>
+  <si>
+    <t>Разложение страницы [1885-1904 выход доноры] модулем InnerMigrationPre1896.</t>
+  </si>
+  <si>
+    <t>Ручная правка для Полтавской и Пензенской губерний для снижения скорости роста и более равномерного распределения.</t>
+  </si>
+  <si>
+    <t>Экстраполяция на 1881-1884 по участку 1885-1892.</t>
+  </si>
+  <si>
+    <t>1881-1904 выход доноры</t>
+  </si>
+  <si>
+    <t>Тобольская</t>
+  </si>
+  <si>
+    <t>Томская</t>
+  </si>
+  <si>
+    <t>Енисейская</t>
+  </si>
+  <si>
+    <t>Иркутская</t>
+  </si>
+  <si>
+    <t>Приморская обл.</t>
+  </si>
+  <si>
+    <t>Акмолинская обл.</t>
+  </si>
+  <si>
+    <t>Семипалатинская обл.</t>
+  </si>
+  <si>
+    <t>Тургайская обл.</t>
+  </si>
+  <si>
+    <t>1894-1896 назначение</t>
+  </si>
+  <si>
+    <t>Я. Ф. Ставровский, В. В. Алексеев. «Переселение в Сибирь». Вып. XVIII. С.-Петербург, 1906. Таблица VII, печатные с. 22–23.</t>
+  </si>
+  <si>
+    <t>куда направлялись переселенцы</t>
+  </si>
+  <si>
+    <t>учёт по охвату становится осмысленным с 1895 года</t>
+  </si>
+  <si>
+    <t>1885-1893%</t>
+  </si>
+  <si>
+    <t>Сведения за 1885-1893</t>
+  </si>
+  <si>
+    <t>Куда направлялись переселенцы</t>
+  </si>
+  <si>
+    <t>Сведения за 1894-1896:</t>
+  </si>
+  <si>
+    <t>С.-Петербург, Государственная типография, 1900, стр. 196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">До 1881 </t>
+  </si>
+  <si>
+    <t>Комитет Сибирской Железной Дороги, "Колонизация Сибири в связи с общим переселенческим вопросом" , издание Канцелярии Комитета Министров,</t>
+  </si>
+  <si>
+    <t>"Переселение в Сибирь"</t>
+  </si>
+  <si>
+    <t>"Колонизация Сибири"</t>
+  </si>
+  <si>
+    <t>Ежегодник ЦСК</t>
+  </si>
+  <si>
+    <t>Ежегодник ЦСК:</t>
+  </si>
+  <si>
+    <t>1908:105</t>
+  </si>
+  <si>
+    <t>1010:784</t>
+  </si>
+  <si>
+    <t>Доп. о колонизации Алтайского округа стр. 336:</t>
+  </si>
+  <si>
+    <t>Амурская обл.</t>
+  </si>
+  <si>
+    <t>Забайкальская обл.</t>
+  </si>
+  <si>
+    <t>Семиреченская обл.</t>
+  </si>
+  <si>
+    <t>1896-1899</t>
+  </si>
+  <si>
+    <t>1896-1899%</t>
+  </si>
+  <si>
+    <t>"Итоги переселенческого движения за время с 1896 по 1909 г."</t>
+  </si>
+  <si>
+    <t>"Итоги переселенческого движения за время с 1896 по 1909 г. "</t>
+  </si>
+  <si>
+    <t>Вывод модуля InnerMigrationShowSum</t>
+  </si>
+  <si>
+    <t>Вывод</t>
+  </si>
+  <si>
+    <t>Для 1895 и более ранних лет следует использовать разбивку "Переселения в Сибирь" на 1895 год</t>
+  </si>
+  <si>
+    <t>как более достоверную сравнительно с другими источниками</t>
+  </si>
+  <si>
+    <t>и согласующуюся с детализованными данными "Итогов переселенческого движения"</t>
+  </si>
+  <si>
+    <t>Я. Ф. Ставровский, В. В. Алексеев. «Переселение в Сибирь». Вып. XVIII. С.-Петербург, 1906. Таблица VII, печатные с. 22–23, тж. см. 24-25</t>
+  </si>
+  <si>
+    <t>% туда</t>
+  </si>
+  <si>
+    <t>% возврата</t>
+  </si>
+  <si>
+    <t>% оседания</t>
+  </si>
+  <si>
+    <t>% туда × % оседания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%туда </t>
+  </si>
+  <si>
+    <t xml:space="preserve">% возврата </t>
+  </si>
+  <si>
+    <t xml:space="preserve">% оседания </t>
+  </si>
+  <si>
+    <t>доля оседающих в ней переселенцев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">последняя колонка </t>
+  </si>
+  <si>
+    <t>даёт часть общего выходного потока оседающего именно в этой области и не возвращающегося из неё</t>
+  </si>
+  <si>
+    <t>доля переселенцев в данную область возвращающихся из неё обратно (вывод модуля RTSS InnerMigrationShowSum, среднее за 1896-1899 гг.)</t>
+  </si>
+  <si>
+    <t>доля общего переселенческого потока направляющуюся в названную область (на 1895 год)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,8 +615,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -470,6 +654,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -600,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -666,6 +856,23 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1000,10 +1207,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5100042B-733C-4FA0-B5DF-69D2DC019B96}">
-  <dimension ref="A1:P110"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P119"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1023,7 +1230,7 @@
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1031,7 +1238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -1039,7 +1246,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -1047,7 +1254,7 @@
         <v>161671</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -1055,7 +1262,7 @@
         <v>932115</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
         <v>9</v>
       </c>
@@ -1063,7 +1270,7 @@
         <v>436584</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
         <v>14</v>
       </c>
@@ -1072,7 +1279,7 @@
         <v>1830370</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
         <v>20</v>
       </c>
@@ -1092,7 +1299,7 @@
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
@@ -1100,7 +1307,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
         <v>5</v>
       </c>
@@ -1108,7 +1315,7 @@
         <v>258154</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B14">
         <v>1893</v>
       </c>
@@ -1116,7 +1323,7 @@
         <v>53350</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B15">
         <v>1894</v>
       </c>
@@ -1124,7 +1331,7 @@
         <v>55776</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B16">
         <v>1895</v>
       </c>
@@ -1132,7 +1339,7 @@
         <v>101995</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B17">
         <f>B16+1</f>
         <v>1896</v>
@@ -1141,7 +1348,7 @@
         <v>186166</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B18">
         <f t="shared" ref="B18:B24" si="0">B17+1</f>
         <v>1897</v>
@@ -1150,7 +1357,7 @@
         <v>81015</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B19">
         <f t="shared" si="0"/>
         <v>1898</v>
@@ -1159,7 +1366,7 @@
         <v>143697</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B20">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -1168,7 +1375,7 @@
         <v>162805</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B21">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -1177,7 +1384,7 @@
         <v>164639</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B22">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -1186,7 +1393,7 @@
         <v>86334</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B23">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -1195,7 +1402,7 @@
         <v>80499</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B24">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -1204,7 +1411,7 @@
         <v>83721</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" t="s">
         <v>14</v>
       </c>
@@ -1213,7 +1420,7 @@
         <v>1458151</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="5" t="s">
         <v>22</v>
       </c>
@@ -1233,7 +1440,7 @@
       <c r="O27" s="4"/>
       <c r="P27" s="4"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="2" t="s">
         <v>1</v>
       </c>
@@ -1241,7 +1448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B30">
         <v>1894</v>
       </c>
@@ -1249,7 +1456,7 @@
         <v>7233</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B31">
         <f>B30+1</f>
         <v>1895</v>
@@ -1258,7 +1465,7 @@
         <v>85933</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B32">
         <f t="shared" ref="B32:B39" si="1">B31+1</f>
         <v>1896</v>
@@ -1267,7 +1474,7 @@
         <v>177168</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B33">
         <f t="shared" si="1"/>
         <v>1897</v>
@@ -1276,7 +1483,7 @@
         <v>66747</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B34">
         <f t="shared" si="1"/>
         <v>1898</v>
@@ -1285,7 +1492,7 @@
         <v>144024</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B35">
         <f t="shared" si="1"/>
         <v>1899</v>
@@ -1294,7 +1501,7 @@
         <v>159747</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B36">
         <f t="shared" si="1"/>
         <v>1900</v>
@@ -1303,7 +1510,7 @@
         <v>152444</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B37">
         <f t="shared" si="1"/>
         <v>1901</v>
@@ -1312,7 +1519,7 @@
         <v>69015</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B38">
         <f t="shared" si="1"/>
         <v>1902</v>
@@ -1321,7 +1528,7 @@
         <v>64550</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B39">
         <f t="shared" si="1"/>
         <v>1903</v>
@@ -1330,7 +1537,7 @@
         <v>71139</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="5" t="s">
         <v>16</v>
       </c>
@@ -1350,7 +1557,7 @@
       <c r="O41" s="4"/>
       <c r="P41" s="4"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="2" t="s">
         <v>1</v>
       </c>
@@ -1358,7 +1565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" t="s">
         <v>6</v>
       </c>
@@ -1366,7 +1573,7 @@
         <v>327100</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" t="s">
         <v>7</v>
       </c>
@@ -1374,7 +1581,7 @@
         <v>495225</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" t="s">
         <v>8</v>
       </c>
@@ -1382,7 +1589,7 @@
         <v>558071</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" t="s">
         <v>14</v>
       </c>
@@ -1391,16 +1598,16 @@
         <v>1380396</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C48" s="3"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" t="s">
         <v>17</v>
       </c>
       <c r="C49" s="3"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" t="s">
         <v>6</v>
       </c>
@@ -1408,7 +1615,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" t="s">
         <v>7</v>
       </c>
@@ -1416,7 +1623,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" t="s">
         <v>8</v>
       </c>
@@ -1424,7 +1631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="5" t="s">
         <v>27</v>
       </c>
@@ -1444,7 +1651,7 @@
       <c r="O54" s="4"/>
       <c r="P54" s="4"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="5" t="s">
         <v>36</v>
       </c>
@@ -1464,7 +1671,7 @@
       <c r="O55" s="4"/>
       <c r="P55" s="4"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C57" s="2" t="s">
         <v>31</v>
       </c>
@@ -1475,7 +1682,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="C58" s="2" t="s">
         <v>34</v>
       </c>
@@ -1484,7 +1691,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="2" t="s">
         <v>11</v>
       </c>
@@ -1498,7 +1705,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B60">
         <v>1896</v>
       </c>
@@ -1513,7 +1720,7 @@
         <v>159882</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B61">
         <v>1897</v>
       </c>
@@ -1528,7 +1735,7 @@
         <v>49685</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B62">
         <v>1898</v>
       </c>
@@ -1543,7 +1750,7 @@
         <v>143704</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B63">
         <v>1899</v>
       </c>
@@ -1558,7 +1765,7 @@
         <v>154942</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B64">
         <v>1900</v>
       </c>
@@ -1573,7 +1780,7 @@
         <v>128752</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B65">
         <v>1901</v>
       </c>
@@ -1588,7 +1795,7 @@
         <v>62932</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B66">
         <v>1902</v>
       </c>
@@ -1603,7 +1810,7 @@
         <v>64808</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B67">
         <v>1903</v>
       </c>
@@ -1618,7 +1825,7 @@
         <v>86875</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="6" t="s">
         <v>24</v>
       </c>
@@ -1638,7 +1845,7 @@
       <c r="O69" s="6"/>
       <c r="P69" s="6"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="6" t="s">
         <v>25</v>
       </c>
@@ -1658,7 +1865,7 @@
       <c r="O70" s="6"/>
       <c r="P70" s="6"/>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="1" t="s">
         <v>11</v>
       </c>
@@ -1684,7 +1891,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B73">
         <f>B74-1</f>
         <v>1881</v>
@@ -1693,7 +1900,7 @@
         <v>6492.9400850000002</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B74">
         <f>B75-1</f>
         <v>1882</v>
@@ -1702,7 +1909,7 @@
         <v>5345.4438110000001</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B75">
         <f>B76-1</f>
         <v>1883</v>
@@ -1711,7 +1918,7 @@
         <v>4174.0546619999996</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B76">
         <f>B77-1</f>
         <v>1884</v>
@@ -1720,7 +1927,7 @@
         <v>3001.3063069999998</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B77">
         <v>1885</v>
       </c>
@@ -1735,7 +1942,7 @@
         <v>22137.742243000001</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B78">
         <f>B77+1</f>
         <v>1886</v>
@@ -1751,7 +1958,7 @@
         <v>22939.139247999999</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B79">
         <f t="shared" ref="B79:B97" si="3">B78+1</f>
         <v>1887</v>
@@ -1767,7 +1974,7 @@
         <v>24614.52692</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B80">
         <f t="shared" si="3"/>
         <v>1888</v>
@@ -1783,7 +1990,7 @@
         <v>27397.393515</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B81">
         <f t="shared" si="3"/>
         <v>1889</v>
@@ -1799,7 +2006,7 @@
         <v>31425.433763000001</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B82">
         <f t="shared" si="3"/>
         <v>1890</v>
@@ -1815,7 +2022,7 @@
         <v>36879.090257000003</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B83">
         <f t="shared" si="3"/>
         <v>1891</v>
@@ -1831,7 +2038,7 @@
         <v>44008.187974</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B84">
         <f t="shared" si="3"/>
         <v>1892</v>
@@ -1847,7 +2054,7 @@
         <v>53145.628228000001</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B85">
         <f t="shared" si="3"/>
         <v>1893</v>
@@ -1863,7 +2070,7 @@
         <v>64552.857853000001</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B86">
         <f t="shared" si="3"/>
         <v>1894</v>
@@ -1881,7 +2088,7 @@
         <v>80226.789336000002</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B87">
         <f t="shared" si="3"/>
         <v>1895</v>
@@ -1899,7 +2106,7 @@
         <v>92405.860002999994</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B88">
         <f t="shared" si="3"/>
         <v>1896</v>
@@ -1927,7 +2134,7 @@
         <v>159882</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B89">
         <f t="shared" si="3"/>
         <v>1897</v>
@@ -1955,7 +2162,7 @@
         <v>49685</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B90">
         <f t="shared" si="3"/>
         <v>1898</v>
@@ -1983,7 +2190,7 @@
         <v>143704</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B91">
         <f t="shared" si="3"/>
         <v>1899</v>
@@ -2011,7 +2218,7 @@
         <v>154942</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B92">
         <f t="shared" si="3"/>
         <v>1900</v>
@@ -2039,7 +2246,7 @@
         <v>128752</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B93">
         <f t="shared" si="3"/>
         <v>1901</v>
@@ -2067,7 +2274,7 @@
         <v>62932</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B94">
         <f t="shared" si="3"/>
         <v>1902</v>
@@ -2095,7 +2302,7 @@
         <v>64808</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B95">
         <f t="shared" si="3"/>
         <v>1903</v>
@@ -2123,7 +2330,7 @@
         <v>86875</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B96">
         <f t="shared" si="3"/>
         <v>1904</v>
@@ -2132,7 +2339,7 @@
         <v>66981.996801999994</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B97">
         <f t="shared" si="3"/>
         <v>1905</v>
@@ -2141,7 +2348,7 @@
         <v>61505.744061999998</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" t="s">
         <v>14</v>
       </c>
@@ -2159,7 +2366,7 @@
         <v>1380395.9999999998</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" t="s">
         <v>15</v>
       </c>
@@ -2180,7 +2387,7 @@
         <v>1380395.9999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" t="s">
         <v>7</v>
       </c>
@@ -2201,7 +2408,7 @@
         <v>495224.99999999994</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" t="s">
         <v>8</v>
       </c>
@@ -2222,19 +2429,19 @@
         <v>558070.99999899999</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B105" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B109" s="26"/>
       <c r="C109" s="26"/>
@@ -2252,9 +2459,74 @@
       <c r="O109" s="26"/>
       <c r="P109" s="26"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B112" s="6"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="6"/>
+      <c r="H112" s="6"/>
+      <c r="I112" s="6"/>
+      <c r="J112" s="6"/>
+      <c r="K112" s="6"/>
+      <c r="L112" s="6"/>
+      <c r="M112" s="6"/>
+      <c r="N112" s="6"/>
+      <c r="O112" s="6"/>
+      <c r="P112" s="6"/>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B117" s="26"/>
+      <c r="C117" s="26"/>
+      <c r="D117" s="26"/>
+      <c r="E117" s="26"/>
+      <c r="F117" s="26"/>
+      <c r="G117" s="26"/>
+      <c r="H117" s="26"/>
+      <c r="I117" s="26"/>
+      <c r="J117" s="26"/>
+      <c r="K117" s="26"/>
+      <c r="L117" s="26"/>
+      <c r="M117" s="26"/>
+      <c r="N117" s="26"/>
+      <c r="O117" s="26"/>
+      <c r="P117" s="26"/>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2266,26 +2538,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF96ABE5-578E-4890-83BE-C69EB8587AC3}">
   <dimension ref="A1:AA58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.15625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7.578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.83984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="7.578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="6.578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="9.83984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.15625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>5</v>
@@ -2351,7 +2623,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="9" t="s">
         <v>51</v>
       </c>
@@ -2435,7 +2707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="12" t="s">
         <v>52</v>
       </c>
@@ -2519,7 +2791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="15" t="s">
         <v>53</v>
       </c>
@@ -2603,7 +2875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="12" t="s">
         <v>54</v>
       </c>
@@ -2687,7 +2959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="15" t="s">
         <v>55</v>
       </c>
@@ -2771,7 +3043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="12" t="s">
         <v>56</v>
       </c>
@@ -2855,7 +3127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="15" t="s">
         <v>57</v>
       </c>
@@ -2939,7 +3211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="12" t="s">
         <v>58</v>
       </c>
@@ -3023,7 +3295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="15" t="s">
         <v>59</v>
       </c>
@@ -3107,7 +3379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="12" t="s">
         <v>60</v>
       </c>
@@ -3191,7 +3463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="15" t="s">
         <v>61</v>
       </c>
@@ -3275,7 +3547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="12" t="s">
         <v>63</v>
       </c>
@@ -3359,7 +3631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="15" t="s">
         <v>64</v>
       </c>
@@ -3443,7 +3715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="12" t="s">
         <v>65</v>
       </c>
@@ -3527,7 +3799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="15" t="s">
         <v>66</v>
       </c>
@@ -3611,7 +3883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="12" t="s">
         <v>67</v>
       </c>
@@ -3695,7 +3967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="15" t="s">
         <v>68</v>
       </c>
@@ -3779,7 +4051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="12" t="s">
         <v>69</v>
       </c>
@@ -3863,7 +4135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="15" t="s">
         <v>70</v>
       </c>
@@ -3947,7 +4219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="12" t="s">
         <v>71</v>
       </c>
@@ -4031,7 +4303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="15" t="s">
         <v>72</v>
       </c>
@@ -4115,7 +4387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="12" t="s">
         <v>73</v>
       </c>
@@ -4199,7 +4471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="15" t="s">
         <v>74</v>
       </c>
@@ -4283,7 +4555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="12" t="s">
         <v>75</v>
       </c>
@@ -4367,7 +4639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="15" t="s">
         <v>76</v>
       </c>
@@ -4451,7 +4723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="12" t="s">
         <v>77</v>
       </c>
@@ -4535,7 +4807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="15" t="s">
         <v>78</v>
       </c>
@@ -4619,7 +4891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="12" t="s">
         <v>79</v>
       </c>
@@ -4703,7 +4975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="15" t="s">
         <v>80</v>
       </c>
@@ -4787,7 +5059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="12" t="s">
         <v>81</v>
       </c>
@@ -4871,7 +5143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="15" t="s">
         <v>82</v>
       </c>
@@ -4955,7 +5227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="12" t="s">
         <v>83</v>
       </c>
@@ -5039,7 +5311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="15" t="s">
         <v>84</v>
       </c>
@@ -5123,7 +5395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="12" t="s">
         <v>85</v>
       </c>
@@ -5207,7 +5479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="15" t="s">
         <v>86</v>
       </c>
@@ -5291,7 +5563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="12" t="s">
         <v>87</v>
       </c>
@@ -5375,7 +5647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="15" t="s">
         <v>88</v>
       </c>
@@ -5459,7 +5731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="12" t="s">
         <v>89</v>
       </c>
@@ -5543,7 +5815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="15" t="s">
         <v>90</v>
       </c>
@@ -5627,7 +5899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="12" t="s">
         <v>91</v>
       </c>
@@ -5711,7 +5983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="15" t="s">
         <v>92</v>
       </c>
@@ -5795,7 +6067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="12" t="s">
         <v>93</v>
       </c>
@@ -5879,7 +6151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="15" t="s">
         <v>94</v>
       </c>
@@ -5963,7 +6235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="12" t="s">
         <v>95</v>
       </c>
@@ -6047,7 +6319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="15" t="s">
         <v>96</v>
       </c>
@@ -6131,7 +6403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="12" t="s">
         <v>97</v>
       </c>
@@ -6215,7 +6487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="15" t="s">
         <v>98</v>
       </c>
@@ -6299,7 +6571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="12" t="s">
         <v>99</v>
       </c>
@@ -6383,7 +6655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="15" t="s">
         <v>100</v>
       </c>
@@ -6467,7 +6739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A51" s="20" t="s">
         <v>101</v>
       </c>
@@ -6545,7 +6817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A52" s="23" t="s">
         <v>110</v>
       </c>
@@ -6613,7 +6885,7 @@
         <v>74402</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="25">
         <f t="shared" ref="B54:V54" si="4">SUM(B2:B51)-B52</f>
         <v>0</v>
@@ -6699,23 +6971,5741 @@
         <v>-0.10000000000582077</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="26" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>113</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A46033-5081-4F58-951C-504380CDA18F}">
+  <dimension ref="A1:AA53"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="15" width="6.20703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="7.20703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.20703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="7.20703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="6.20703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="34">
+        <v>1881</v>
+      </c>
+      <c r="C1" s="34">
+        <v>1882</v>
+      </c>
+      <c r="D1" s="34">
+        <v>1883</v>
+      </c>
+      <c r="E1" s="34">
+        <v>1884</v>
+      </c>
+      <c r="F1" s="34">
+        <v>1885</v>
+      </c>
+      <c r="G1" s="34">
+        <v>1886</v>
+      </c>
+      <c r="H1" s="34">
+        <v>1887</v>
+      </c>
+      <c r="I1" s="34">
+        <v>1888</v>
+      </c>
+      <c r="J1" s="34">
+        <v>1889</v>
+      </c>
+      <c r="K1" s="34">
+        <v>1890</v>
+      </c>
+      <c r="L1" s="34">
+        <v>1891</v>
+      </c>
+      <c r="M1" s="34">
+        <v>1892</v>
+      </c>
+      <c r="N1" s="34">
+        <v>1893</v>
+      </c>
+      <c r="O1" s="34">
+        <v>1894</v>
+      </c>
+      <c r="P1" s="34">
+        <v>1895</v>
+      </c>
+      <c r="Q1" s="34">
+        <v>1896</v>
+      </c>
+      <c r="R1" s="34">
+        <v>1897</v>
+      </c>
+      <c r="S1" s="34">
+        <v>1898</v>
+      </c>
+      <c r="T1" s="34">
+        <v>1899</v>
+      </c>
+      <c r="U1" s="34">
+        <v>1900</v>
+      </c>
+      <c r="V1" s="34">
+        <v>1901</v>
+      </c>
+      <c r="W1" s="34">
+        <v>1902</v>
+      </c>
+      <c r="X1" s="34">
+        <v>1903</v>
+      </c>
+      <c r="Y1" s="34">
+        <v>1904</v>
+      </c>
+      <c r="AA1" s="2"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2">
+        <v>8292</v>
+      </c>
+      <c r="C2">
+        <v>8292</v>
+      </c>
+      <c r="D2">
+        <v>8292</v>
+      </c>
+      <c r="E2">
+        <v>8292</v>
+      </c>
+      <c r="F2">
+        <v>8292</v>
+      </c>
+      <c r="G2">
+        <v>8292</v>
+      </c>
+      <c r="H2">
+        <v>8292</v>
+      </c>
+      <c r="I2">
+        <v>8292</v>
+      </c>
+      <c r="J2">
+        <v>8292</v>
+      </c>
+      <c r="K2">
+        <v>8292</v>
+      </c>
+      <c r="L2">
+        <v>8292</v>
+      </c>
+      <c r="M2">
+        <v>8292</v>
+      </c>
+      <c r="N2">
+        <v>4108</v>
+      </c>
+      <c r="O2">
+        <v>4943</v>
+      </c>
+      <c r="P2">
+        <v>8940</v>
+      </c>
+      <c r="Q2">
+        <v>14298</v>
+      </c>
+      <c r="R2">
+        <v>4273</v>
+      </c>
+      <c r="S2">
+        <v>9194</v>
+      </c>
+      <c r="T2">
+        <v>13656</v>
+      </c>
+      <c r="U2">
+        <v>16278</v>
+      </c>
+      <c r="V2">
+        <v>5410</v>
+      </c>
+      <c r="W2">
+        <v>2139</v>
+      </c>
+      <c r="X2">
+        <v>1662</v>
+      </c>
+      <c r="Y2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3">
+        <v>4560</v>
+      </c>
+      <c r="C3">
+        <v>4566</v>
+      </c>
+      <c r="D3">
+        <v>4573</v>
+      </c>
+      <c r="E3">
+        <v>4581</v>
+      </c>
+      <c r="F3">
+        <v>4598</v>
+      </c>
+      <c r="G3">
+        <v>4603</v>
+      </c>
+      <c r="H3">
+        <v>4614</v>
+      </c>
+      <c r="I3">
+        <v>4632</v>
+      </c>
+      <c r="J3">
+        <v>4657</v>
+      </c>
+      <c r="K3">
+        <v>4690</v>
+      </c>
+      <c r="L3">
+        <v>4732</v>
+      </c>
+      <c r="M3">
+        <v>4752</v>
+      </c>
+      <c r="N3">
+        <v>5087</v>
+      </c>
+      <c r="O3">
+        <v>3605</v>
+      </c>
+      <c r="P3">
+        <v>3208</v>
+      </c>
+      <c r="Q3">
+        <v>6693</v>
+      </c>
+      <c r="R3">
+        <v>3604</v>
+      </c>
+      <c r="S3">
+        <v>14689</v>
+      </c>
+      <c r="T3">
+        <v>14331</v>
+      </c>
+      <c r="U3">
+        <v>5610</v>
+      </c>
+      <c r="V3">
+        <v>2081</v>
+      </c>
+      <c r="W3">
+        <v>1868</v>
+      </c>
+      <c r="X3">
+        <v>2003</v>
+      </c>
+      <c r="Y3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4">
+        <v>267</v>
+      </c>
+      <c r="C4">
+        <v>270</v>
+      </c>
+      <c r="D4">
+        <v>275</v>
+      </c>
+      <c r="E4">
+        <v>283</v>
+      </c>
+      <c r="F4" s="28">
+        <v>300</v>
+      </c>
+      <c r="G4" s="28">
+        <v>320</v>
+      </c>
+      <c r="H4" s="28">
+        <v>360</v>
+      </c>
+      <c r="I4" s="28">
+        <v>420</v>
+      </c>
+      <c r="J4" s="28">
+        <v>550</v>
+      </c>
+      <c r="K4" s="28">
+        <v>750</v>
+      </c>
+      <c r="L4" s="28">
+        <v>1100</v>
+      </c>
+      <c r="M4" s="28">
+        <v>1693</v>
+      </c>
+      <c r="N4">
+        <v>2951</v>
+      </c>
+      <c r="O4">
+        <v>851</v>
+      </c>
+      <c r="P4">
+        <v>23113</v>
+      </c>
+      <c r="Q4">
+        <v>5293</v>
+      </c>
+      <c r="R4">
+        <v>1100</v>
+      </c>
+      <c r="S4">
+        <v>3100</v>
+      </c>
+      <c r="T4">
+        <v>5449</v>
+      </c>
+      <c r="U4">
+        <v>2763</v>
+      </c>
+      <c r="V4">
+        <v>1097</v>
+      </c>
+      <c r="W4">
+        <v>1025</v>
+      </c>
+      <c r="X4">
+        <v>1526</v>
+      </c>
+      <c r="Y4">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5">
+        <v>306</v>
+      </c>
+      <c r="C5">
+        <v>317</v>
+      </c>
+      <c r="D5">
+        <v>332</v>
+      </c>
+      <c r="E5">
+        <v>354</v>
+      </c>
+      <c r="F5">
+        <v>401</v>
+      </c>
+      <c r="G5">
+        <v>426</v>
+      </c>
+      <c r="H5">
+        <v>480</v>
+      </c>
+      <c r="I5">
+        <v>571</v>
+      </c>
+      <c r="J5">
+        <v>708</v>
+      </c>
+      <c r="K5">
+        <v>900</v>
+      </c>
+      <c r="L5">
+        <v>1164</v>
+      </c>
+      <c r="M5">
+        <v>1516</v>
+      </c>
+      <c r="N5">
+        <v>2049</v>
+      </c>
+      <c r="O5">
+        <v>2228</v>
+      </c>
+      <c r="P5">
+        <v>4898</v>
+      </c>
+      <c r="Q5">
+        <v>15987</v>
+      </c>
+      <c r="R5">
+        <v>5848</v>
+      </c>
+      <c r="S5">
+        <v>11258</v>
+      </c>
+      <c r="T5">
+        <v>7137</v>
+      </c>
+      <c r="U5">
+        <v>3871</v>
+      </c>
+      <c r="V5">
+        <v>2313</v>
+      </c>
+      <c r="W5">
+        <v>1518</v>
+      </c>
+      <c r="X5">
+        <v>1628</v>
+      </c>
+      <c r="Y5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6">
+        <v>85</v>
+      </c>
+      <c r="C6">
+        <v>91</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>116</v>
+      </c>
+      <c r="F6">
+        <v>155</v>
+      </c>
+      <c r="G6">
+        <v>184</v>
+      </c>
+      <c r="H6">
+        <v>249</v>
+      </c>
+      <c r="I6">
+        <v>372</v>
+      </c>
+      <c r="J6">
+        <v>580</v>
+      </c>
+      <c r="K6">
+        <v>922</v>
+      </c>
+      <c r="L6">
+        <v>1475</v>
+      </c>
+      <c r="M6">
+        <v>2398</v>
+      </c>
+      <c r="N6">
+        <v>3612</v>
+      </c>
+      <c r="O6">
+        <v>6972</v>
+      </c>
+      <c r="P6">
+        <v>15135</v>
+      </c>
+      <c r="Q6">
+        <v>36198</v>
+      </c>
+      <c r="R6">
+        <v>11640</v>
+      </c>
+      <c r="S6">
+        <v>5874</v>
+      </c>
+      <c r="T6">
+        <v>6205</v>
+      </c>
+      <c r="U6">
+        <v>11400</v>
+      </c>
+      <c r="V6">
+        <v>8883</v>
+      </c>
+      <c r="W6">
+        <v>6283</v>
+      </c>
+      <c r="X6">
+        <v>4149</v>
+      </c>
+      <c r="Y6">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
+        <v>47</v>
+      </c>
+      <c r="M7">
+        <v>134</v>
+      </c>
+      <c r="N7">
+        <v>456</v>
+      </c>
+      <c r="O7">
+        <v>1102</v>
+      </c>
+      <c r="P7">
+        <v>1743</v>
+      </c>
+      <c r="Q7">
+        <v>7819</v>
+      </c>
+      <c r="R7">
+        <v>1574</v>
+      </c>
+      <c r="S7">
+        <v>5816</v>
+      </c>
+      <c r="T7">
+        <v>3271</v>
+      </c>
+      <c r="U7">
+        <v>1058</v>
+      </c>
+      <c r="V7">
+        <v>461</v>
+      </c>
+      <c r="W7">
+        <v>427</v>
+      </c>
+      <c r="X7">
+        <v>259</v>
+      </c>
+      <c r="Y7">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8">
+        <v>631</v>
+      </c>
+      <c r="C8">
+        <v>651</v>
+      </c>
+      <c r="D8">
+        <v>679</v>
+      </c>
+      <c r="E8">
+        <v>717</v>
+      </c>
+      <c r="F8">
+        <v>798</v>
+      </c>
+      <c r="G8">
+        <v>835</v>
+      </c>
+      <c r="H8">
+        <v>913</v>
+      </c>
+      <c r="I8">
+        <v>1044</v>
+      </c>
+      <c r="J8">
+        <v>1236</v>
+      </c>
+      <c r="K8">
+        <v>1500</v>
+      </c>
+      <c r="L8">
+        <v>1854</v>
+      </c>
+      <c r="M8">
+        <v>2253</v>
+      </c>
+      <c r="N8">
+        <v>3438</v>
+      </c>
+      <c r="O8">
+        <v>762</v>
+      </c>
+      <c r="P8">
+        <v>2525</v>
+      </c>
+      <c r="Q8">
+        <v>2512</v>
+      </c>
+      <c r="R8">
+        <v>1251</v>
+      </c>
+      <c r="S8">
+        <v>5247</v>
+      </c>
+      <c r="T8">
+        <v>4116</v>
+      </c>
+      <c r="U8">
+        <v>1073</v>
+      </c>
+      <c r="V8">
+        <v>447</v>
+      </c>
+      <c r="W8">
+        <v>460</v>
+      </c>
+      <c r="X8">
+        <v>358</v>
+      </c>
+      <c r="Y8">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9">
+        <v>134</v>
+      </c>
+      <c r="C9">
+        <v>141</v>
+      </c>
+      <c r="D9">
+        <v>152</v>
+      </c>
+      <c r="E9">
+        <v>170</v>
+      </c>
+      <c r="F9" s="28">
+        <v>200</v>
+      </c>
+      <c r="G9" s="28">
+        <v>250</v>
+      </c>
+      <c r="H9" s="28">
+        <v>350</v>
+      </c>
+      <c r="I9" s="28">
+        <v>500</v>
+      </c>
+      <c r="J9" s="28">
+        <v>750</v>
+      </c>
+      <c r="K9" s="28">
+        <v>1200</v>
+      </c>
+      <c r="L9" s="28">
+        <v>2500</v>
+      </c>
+      <c r="M9" s="28">
+        <v>5743</v>
+      </c>
+      <c r="N9">
+        <v>11468</v>
+      </c>
+      <c r="O9">
+        <v>26029</v>
+      </c>
+      <c r="P9">
+        <v>18841</v>
+      </c>
+      <c r="Q9">
+        <v>38819</v>
+      </c>
+      <c r="R9">
+        <v>7932</v>
+      </c>
+      <c r="S9">
+        <v>4310</v>
+      </c>
+      <c r="T9">
+        <v>10711</v>
+      </c>
+      <c r="U9">
+        <v>26632</v>
+      </c>
+      <c r="V9">
+        <v>12063</v>
+      </c>
+      <c r="W9">
+        <v>10412</v>
+      </c>
+      <c r="X9">
+        <v>7892</v>
+      </c>
+      <c r="Y9">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10">
+        <v>958</v>
+      </c>
+      <c r="C10">
+        <v>967</v>
+      </c>
+      <c r="D10">
+        <v>980</v>
+      </c>
+      <c r="E10">
+        <v>996</v>
+      </c>
+      <c r="F10">
+        <v>1029</v>
+      </c>
+      <c r="G10">
+        <v>1045</v>
+      </c>
+      <c r="H10">
+        <v>1078</v>
+      </c>
+      <c r="I10">
+        <v>1131</v>
+      </c>
+      <c r="J10">
+        <v>1207</v>
+      </c>
+      <c r="K10">
+        <v>1306</v>
+      </c>
+      <c r="L10">
+        <v>1431</v>
+      </c>
+      <c r="M10">
+        <v>1580</v>
+      </c>
+      <c r="N10">
+        <v>1811</v>
+      </c>
+      <c r="O10">
+        <v>1706</v>
+      </c>
+      <c r="P10">
+        <v>2739</v>
+      </c>
+      <c r="Q10">
+        <v>8497</v>
+      </c>
+      <c r="R10">
+        <v>3152</v>
+      </c>
+      <c r="S10">
+        <v>3497</v>
+      </c>
+      <c r="T10">
+        <v>6833</v>
+      </c>
+      <c r="U10">
+        <v>11141</v>
+      </c>
+      <c r="V10">
+        <v>3182</v>
+      </c>
+      <c r="W10">
+        <v>3374</v>
+      </c>
+      <c r="X10">
+        <v>3106</v>
+      </c>
+      <c r="Y10">
+        <v>2616</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11">
+        <v>1660</v>
+      </c>
+      <c r="C11">
+        <v>1694</v>
+      </c>
+      <c r="D11">
+        <v>1741</v>
+      </c>
+      <c r="E11">
+        <v>1803</v>
+      </c>
+      <c r="F11">
+        <v>1933</v>
+      </c>
+      <c r="G11">
+        <v>1994</v>
+      </c>
+      <c r="H11">
+        <v>2121</v>
+      </c>
+      <c r="I11">
+        <v>2331</v>
+      </c>
+      <c r="J11">
+        <v>2633</v>
+      </c>
+      <c r="K11">
+        <v>3039</v>
+      </c>
+      <c r="L11">
+        <v>3568</v>
+      </c>
+      <c r="M11">
+        <v>4178</v>
+      </c>
+      <c r="N11">
+        <v>5555</v>
+      </c>
+      <c r="O11">
+        <v>3605</v>
+      </c>
+      <c r="P11">
+        <v>3271</v>
+      </c>
+      <c r="Q11">
+        <v>5540</v>
+      </c>
+      <c r="R11">
+        <v>4423</v>
+      </c>
+      <c r="S11">
+        <v>7043</v>
+      </c>
+      <c r="T11">
+        <v>9919</v>
+      </c>
+      <c r="U11">
+        <v>8200</v>
+      </c>
+      <c r="V11">
+        <v>2124</v>
+      </c>
+      <c r="W11">
+        <v>2809</v>
+      </c>
+      <c r="X11">
+        <v>3705</v>
+      </c>
+      <c r="Y11">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>46</v>
+      </c>
+      <c r="P12">
+        <v>313</v>
+      </c>
+      <c r="Q12">
+        <v>1967</v>
+      </c>
+      <c r="R12">
+        <v>1318</v>
+      </c>
+      <c r="S12">
+        <v>3539</v>
+      </c>
+      <c r="T12">
+        <v>3428</v>
+      </c>
+      <c r="U12">
+        <v>3636</v>
+      </c>
+      <c r="V12">
+        <v>3195</v>
+      </c>
+      <c r="W12">
+        <v>3523</v>
+      </c>
+      <c r="X12">
+        <v>1704</v>
+      </c>
+      <c r="Y12">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>64</v>
+      </c>
+      <c r="Q13">
+        <v>137</v>
+      </c>
+      <c r="R13">
+        <v>364</v>
+      </c>
+      <c r="S13">
+        <v>123</v>
+      </c>
+      <c r="T13">
+        <v>148</v>
+      </c>
+      <c r="U13">
+        <v>1253</v>
+      </c>
+      <c r="V13">
+        <v>2026</v>
+      </c>
+      <c r="W13">
+        <v>2356</v>
+      </c>
+      <c r="X13">
+        <v>1028</v>
+      </c>
+      <c r="Y13">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>428</v>
+      </c>
+      <c r="R14">
+        <v>921</v>
+      </c>
+      <c r="S14">
+        <v>992</v>
+      </c>
+      <c r="T14">
+        <v>1408</v>
+      </c>
+      <c r="U14">
+        <v>2006</v>
+      </c>
+      <c r="V14">
+        <v>1938</v>
+      </c>
+      <c r="W14">
+        <v>863</v>
+      </c>
+      <c r="X14">
+        <v>960</v>
+      </c>
+      <c r="Y14">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>320</v>
+      </c>
+      <c r="Q15">
+        <v>798</v>
+      </c>
+      <c r="R15">
+        <v>243</v>
+      </c>
+      <c r="S15">
+        <v>95</v>
+      </c>
+      <c r="T15">
+        <v>114</v>
+      </c>
+      <c r="U15">
+        <v>558</v>
+      </c>
+      <c r="V15">
+        <v>355</v>
+      </c>
+      <c r="W15">
+        <v>727</v>
+      </c>
+      <c r="X15">
+        <v>574</v>
+      </c>
+      <c r="Y15">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>49</v>
+      </c>
+      <c r="P16">
+        <v>159</v>
+      </c>
+      <c r="Q16">
+        <v>1969</v>
+      </c>
+      <c r="R16">
+        <v>2305</v>
+      </c>
+      <c r="S16">
+        <v>1243</v>
+      </c>
+      <c r="T16">
+        <v>2325</v>
+      </c>
+      <c r="U16">
+        <v>5562</v>
+      </c>
+      <c r="V16">
+        <v>4872</v>
+      </c>
+      <c r="W16">
+        <v>4858</v>
+      </c>
+      <c r="X16">
+        <v>4028</v>
+      </c>
+      <c r="Y16">
+        <v>2977</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>3</v>
+      </c>
+      <c r="P17">
+        <v>587</v>
+      </c>
+      <c r="Q17">
+        <v>3762</v>
+      </c>
+      <c r="R17">
+        <v>3735</v>
+      </c>
+      <c r="S17">
+        <v>1315</v>
+      </c>
+      <c r="T17">
+        <v>2607</v>
+      </c>
+      <c r="U17">
+        <v>4191</v>
+      </c>
+      <c r="V17">
+        <v>3192</v>
+      </c>
+      <c r="W17">
+        <v>2488</v>
+      </c>
+      <c r="X17">
+        <v>2396</v>
+      </c>
+      <c r="Y17">
+        <v>5263</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>59</v>
+      </c>
+      <c r="P18">
+        <v>104</v>
+      </c>
+      <c r="Q18">
+        <v>150</v>
+      </c>
+      <c r="R18">
+        <v>712</v>
+      </c>
+      <c r="S18">
+        <v>749</v>
+      </c>
+      <c r="T18">
+        <v>1510</v>
+      </c>
+      <c r="U18">
+        <v>3117</v>
+      </c>
+      <c r="V18">
+        <v>3265</v>
+      </c>
+      <c r="W18">
+        <v>3721</v>
+      </c>
+      <c r="X18">
+        <v>2781</v>
+      </c>
+      <c r="Y18">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>26</v>
+      </c>
+      <c r="P19">
+        <v>823</v>
+      </c>
+      <c r="Q19">
+        <v>843</v>
+      </c>
+      <c r="R19">
+        <v>533</v>
+      </c>
+      <c r="S19">
+        <v>657</v>
+      </c>
+      <c r="T19">
+        <v>1265</v>
+      </c>
+      <c r="U19">
+        <v>1764</v>
+      </c>
+      <c r="V19">
+        <v>478</v>
+      </c>
+      <c r="W19">
+        <v>745</v>
+      </c>
+      <c r="X19">
+        <v>681</v>
+      </c>
+      <c r="Y19">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>11</v>
+      </c>
+      <c r="P20">
+        <v>194</v>
+      </c>
+      <c r="Q20">
+        <v>190</v>
+      </c>
+      <c r="R20">
+        <v>23</v>
+      </c>
+      <c r="S20">
+        <v>24</v>
+      </c>
+      <c r="T20">
+        <v>64</v>
+      </c>
+      <c r="U20">
+        <v>81</v>
+      </c>
+      <c r="V20">
+        <v>17</v>
+      </c>
+      <c r="W20">
+        <v>37</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21">
+        <v>1060</v>
+      </c>
+      <c r="C21">
+        <v>1060</v>
+      </c>
+      <c r="D21">
+        <v>1060</v>
+      </c>
+      <c r="E21">
+        <v>1060</v>
+      </c>
+      <c r="F21">
+        <v>1060</v>
+      </c>
+      <c r="G21">
+        <v>1060</v>
+      </c>
+      <c r="H21">
+        <v>1060</v>
+      </c>
+      <c r="I21">
+        <v>1060</v>
+      </c>
+      <c r="J21">
+        <v>1060</v>
+      </c>
+      <c r="K21">
+        <v>1060</v>
+      </c>
+      <c r="L21">
+        <v>1060</v>
+      </c>
+      <c r="M21">
+        <v>1060</v>
+      </c>
+      <c r="N21">
+        <v>1056</v>
+      </c>
+      <c r="O21">
+        <v>450</v>
+      </c>
+      <c r="P21">
+        <v>537</v>
+      </c>
+      <c r="Q21">
+        <v>675</v>
+      </c>
+      <c r="R21">
+        <v>205</v>
+      </c>
+      <c r="S21">
+        <v>1531</v>
+      </c>
+      <c r="T21">
+        <v>2220</v>
+      </c>
+      <c r="U21">
+        <v>539</v>
+      </c>
+      <c r="V21">
+        <v>247</v>
+      </c>
+      <c r="W21">
+        <v>217</v>
+      </c>
+      <c r="X21">
+        <v>464</v>
+      </c>
+      <c r="Y21">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22">
+        <v>702</v>
+      </c>
+      <c r="C22">
+        <v>702</v>
+      </c>
+      <c r="D22">
+        <v>702</v>
+      </c>
+      <c r="E22">
+        <v>702</v>
+      </c>
+      <c r="F22">
+        <v>702</v>
+      </c>
+      <c r="G22">
+        <v>702</v>
+      </c>
+      <c r="H22">
+        <v>702</v>
+      </c>
+      <c r="I22">
+        <v>702</v>
+      </c>
+      <c r="J22">
+        <v>702</v>
+      </c>
+      <c r="K22">
+        <v>702</v>
+      </c>
+      <c r="L22">
+        <v>702</v>
+      </c>
+      <c r="M22">
+        <v>702</v>
+      </c>
+      <c r="N22">
+        <v>517</v>
+      </c>
+      <c r="O22">
+        <v>146</v>
+      </c>
+      <c r="P22">
+        <v>425</v>
+      </c>
+      <c r="Q22">
+        <v>528</v>
+      </c>
+      <c r="R22">
+        <v>151</v>
+      </c>
+      <c r="S22">
+        <v>454</v>
+      </c>
+      <c r="T22">
+        <v>833</v>
+      </c>
+      <c r="U22">
+        <v>378</v>
+      </c>
+      <c r="V22">
+        <v>208</v>
+      </c>
+      <c r="W22">
+        <v>101</v>
+      </c>
+      <c r="X22">
+        <v>104</v>
+      </c>
+      <c r="Y22">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23">
+        <v>324</v>
+      </c>
+      <c r="C23">
+        <v>331</v>
+      </c>
+      <c r="D23">
+        <v>340</v>
+      </c>
+      <c r="E23">
+        <v>352</v>
+      </c>
+      <c r="F23">
+        <v>378</v>
+      </c>
+      <c r="G23">
+        <v>390</v>
+      </c>
+      <c r="H23">
+        <v>415</v>
+      </c>
+      <c r="I23">
+        <v>457</v>
+      </c>
+      <c r="J23">
+        <v>516</v>
+      </c>
+      <c r="K23">
+        <v>596</v>
+      </c>
+      <c r="L23">
+        <v>700</v>
+      </c>
+      <c r="M23">
+        <v>820</v>
+      </c>
+      <c r="N23">
+        <v>1113</v>
+      </c>
+      <c r="O23">
+        <v>474</v>
+      </c>
+      <c r="P23">
+        <v>2241</v>
+      </c>
+      <c r="Q23">
+        <v>2120</v>
+      </c>
+      <c r="R23">
+        <v>286</v>
+      </c>
+      <c r="S23">
+        <v>2188</v>
+      </c>
+      <c r="T23">
+        <v>4365</v>
+      </c>
+      <c r="U23">
+        <v>1370</v>
+      </c>
+      <c r="V23">
+        <v>388</v>
+      </c>
+      <c r="W23">
+        <v>362</v>
+      </c>
+      <c r="X23">
+        <v>498</v>
+      </c>
+      <c r="Y23">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24">
+        <v>1136</v>
+      </c>
+      <c r="C24">
+        <v>1139</v>
+      </c>
+      <c r="D24">
+        <v>1144</v>
+      </c>
+      <c r="E24">
+        <v>1149</v>
+      </c>
+      <c r="F24">
+        <v>1159</v>
+      </c>
+      <c r="G24">
+        <v>1162</v>
+      </c>
+      <c r="H24">
+        <v>1169</v>
+      </c>
+      <c r="I24">
+        <v>1179</v>
+      </c>
+      <c r="J24">
+        <v>1194</v>
+      </c>
+      <c r="K24">
+        <v>1213</v>
+      </c>
+      <c r="L24">
+        <v>1237</v>
+      </c>
+      <c r="M24">
+        <v>1247</v>
+      </c>
+      <c r="N24">
+        <v>1453</v>
+      </c>
+      <c r="O24">
+        <v>403</v>
+      </c>
+      <c r="P24">
+        <v>1867</v>
+      </c>
+      <c r="Q24">
+        <v>3310</v>
+      </c>
+      <c r="R24">
+        <v>1228</v>
+      </c>
+      <c r="S24">
+        <v>3133</v>
+      </c>
+      <c r="T24">
+        <v>7128</v>
+      </c>
+      <c r="U24">
+        <v>3000</v>
+      </c>
+      <c r="V24">
+        <v>807</v>
+      </c>
+      <c r="W24">
+        <v>991</v>
+      </c>
+      <c r="X24">
+        <v>1652</v>
+      </c>
+      <c r="Y24">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25">
+        <v>663</v>
+      </c>
+      <c r="C25">
+        <v>663</v>
+      </c>
+      <c r="D25">
+        <v>663</v>
+      </c>
+      <c r="E25">
+        <v>663</v>
+      </c>
+      <c r="F25">
+        <v>663</v>
+      </c>
+      <c r="G25">
+        <v>663</v>
+      </c>
+      <c r="H25">
+        <v>662</v>
+      </c>
+      <c r="I25">
+        <v>662</v>
+      </c>
+      <c r="J25">
+        <v>661</v>
+      </c>
+      <c r="K25">
+        <v>660</v>
+      </c>
+      <c r="L25">
+        <v>658</v>
+      </c>
+      <c r="M25">
+        <v>667</v>
+      </c>
+      <c r="N25">
+        <v>591</v>
+      </c>
+      <c r="O25">
+        <v>794</v>
+      </c>
+      <c r="P25">
+        <v>3813</v>
+      </c>
+      <c r="Q25">
+        <v>3935</v>
+      </c>
+      <c r="R25">
+        <v>1401</v>
+      </c>
+      <c r="S25">
+        <v>13523</v>
+      </c>
+      <c r="T25">
+        <v>19984</v>
+      </c>
+      <c r="U25">
+        <v>4665</v>
+      </c>
+      <c r="V25">
+        <v>905</v>
+      </c>
+      <c r="W25">
+        <v>1323</v>
+      </c>
+      <c r="X25">
+        <v>1597</v>
+      </c>
+      <c r="Y25">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>28</v>
+      </c>
+      <c r="P26">
+        <v>168</v>
+      </c>
+      <c r="Q26">
+        <v>806</v>
+      </c>
+      <c r="R26">
+        <v>416</v>
+      </c>
+      <c r="S26">
+        <v>1927</v>
+      </c>
+      <c r="T26">
+        <v>1938</v>
+      </c>
+      <c r="U26">
+        <v>1114</v>
+      </c>
+      <c r="V26">
+        <v>171</v>
+      </c>
+      <c r="W26">
+        <v>290</v>
+      </c>
+      <c r="X26">
+        <v>548</v>
+      </c>
+      <c r="Y26">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>14</v>
+      </c>
+      <c r="P27">
+        <v>37</v>
+      </c>
+      <c r="Q27">
+        <v>140</v>
+      </c>
+      <c r="R27">
+        <v>298</v>
+      </c>
+      <c r="S27">
+        <v>392</v>
+      </c>
+      <c r="T27">
+        <v>665</v>
+      </c>
+      <c r="U27">
+        <v>249</v>
+      </c>
+      <c r="V27">
+        <v>125</v>
+      </c>
+      <c r="W27">
+        <v>120</v>
+      </c>
+      <c r="X27">
+        <v>164</v>
+      </c>
+      <c r="Y27">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>4</v>
+      </c>
+      <c r="R28">
+        <v>4</v>
+      </c>
+      <c r="S28">
+        <v>27</v>
+      </c>
+      <c r="T28">
+        <v>48</v>
+      </c>
+      <c r="U28">
+        <v>17</v>
+      </c>
+      <c r="V28">
+        <v>1</v>
+      </c>
+      <c r="W28">
+        <v>1</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>6</v>
+      </c>
+      <c r="P29">
+        <v>12</v>
+      </c>
+      <c r="Q29">
+        <v>915</v>
+      </c>
+      <c r="R29">
+        <v>1467</v>
+      </c>
+      <c r="S29">
+        <v>1396</v>
+      </c>
+      <c r="T29">
+        <v>524</v>
+      </c>
+      <c r="U29">
+        <v>331</v>
+      </c>
+      <c r="V29">
+        <v>162</v>
+      </c>
+      <c r="W29">
+        <v>58</v>
+      </c>
+      <c r="X29">
+        <v>128</v>
+      </c>
+      <c r="Y29">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>13</v>
+      </c>
+      <c r="P30">
+        <v>8</v>
+      </c>
+      <c r="Q30">
+        <v>37</v>
+      </c>
+      <c r="R30">
+        <v>8</v>
+      </c>
+      <c r="S30">
+        <v>42</v>
+      </c>
+      <c r="T30">
+        <v>126</v>
+      </c>
+      <c r="U30">
+        <v>40</v>
+      </c>
+      <c r="V30">
+        <v>18</v>
+      </c>
+      <c r="W30">
+        <v>14</v>
+      </c>
+      <c r="X30">
+        <v>12</v>
+      </c>
+      <c r="Y30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>1</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>2</v>
+      </c>
+      <c r="T31">
+        <v>5</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>224</v>
+      </c>
+      <c r="R32">
+        <v>244</v>
+      </c>
+      <c r="S32">
+        <v>19</v>
+      </c>
+      <c r="T32">
+        <v>29</v>
+      </c>
+      <c r="U32">
+        <v>140</v>
+      </c>
+      <c r="V32">
+        <v>182</v>
+      </c>
+      <c r="W32">
+        <v>15</v>
+      </c>
+      <c r="X32">
+        <v>45</v>
+      </c>
+      <c r="Y32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33">
+        <v>89</v>
+      </c>
+      <c r="C33">
+        <v>88</v>
+      </c>
+      <c r="D33">
+        <v>85</v>
+      </c>
+      <c r="E33">
+        <v>83</v>
+      </c>
+      <c r="F33">
+        <v>78</v>
+      </c>
+      <c r="G33">
+        <v>76</v>
+      </c>
+      <c r="H33">
+        <v>72</v>
+      </c>
+      <c r="I33">
+        <v>65</v>
+      </c>
+      <c r="J33">
+        <v>57</v>
+      </c>
+      <c r="K33">
+        <v>46</v>
+      </c>
+      <c r="L33">
+        <v>34</v>
+      </c>
+      <c r="M33">
+        <v>22</v>
+      </c>
+      <c r="N33">
+        <v>5</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>103</v>
+      </c>
+      <c r="Q33">
+        <v>3900</v>
+      </c>
+      <c r="R33">
+        <v>2187</v>
+      </c>
+      <c r="S33">
+        <v>1422</v>
+      </c>
+      <c r="T33">
+        <v>596</v>
+      </c>
+      <c r="U33">
+        <v>1438</v>
+      </c>
+      <c r="V33">
+        <v>2272</v>
+      </c>
+      <c r="W33">
+        <v>912</v>
+      </c>
+      <c r="X33">
+        <v>1481</v>
+      </c>
+      <c r="Y33">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34">
+        <v>51</v>
+      </c>
+      <c r="C34">
+        <v>51</v>
+      </c>
+      <c r="D34">
+        <v>51</v>
+      </c>
+      <c r="E34">
+        <v>51</v>
+      </c>
+      <c r="F34">
+        <v>51</v>
+      </c>
+      <c r="G34">
+        <v>51</v>
+      </c>
+      <c r="H34">
+        <v>51</v>
+      </c>
+      <c r="I34">
+        <v>51</v>
+      </c>
+      <c r="J34">
+        <v>51</v>
+      </c>
+      <c r="K34">
+        <v>51</v>
+      </c>
+      <c r="L34">
+        <v>51</v>
+      </c>
+      <c r="M34">
+        <v>51</v>
+      </c>
+      <c r="N34">
+        <v>63</v>
+      </c>
+      <c r="O34">
+        <v>28</v>
+      </c>
+      <c r="P34">
+        <v>187</v>
+      </c>
+      <c r="Q34">
+        <v>1938</v>
+      </c>
+      <c r="R34">
+        <v>433</v>
+      </c>
+      <c r="S34">
+        <v>2445</v>
+      </c>
+      <c r="T34">
+        <v>2786</v>
+      </c>
+      <c r="U34">
+        <v>2795</v>
+      </c>
+      <c r="V34">
+        <v>943</v>
+      </c>
+      <c r="W34">
+        <v>652</v>
+      </c>
+      <c r="X34">
+        <v>904</v>
+      </c>
+      <c r="Y34">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35">
+        <v>3</v>
+      </c>
+      <c r="J35">
+        <v>5</v>
+      </c>
+      <c r="K35">
+        <v>8</v>
+      </c>
+      <c r="L35">
+        <v>15</v>
+      </c>
+      <c r="M35">
+        <v>26</v>
+      </c>
+      <c r="N35">
+        <v>59</v>
+      </c>
+      <c r="O35">
+        <v>15</v>
+      </c>
+      <c r="P35">
+        <v>191</v>
+      </c>
+      <c r="Q35">
+        <v>538</v>
+      </c>
+      <c r="R35">
+        <v>878</v>
+      </c>
+      <c r="S35">
+        <v>5656</v>
+      </c>
+      <c r="T35">
+        <v>1927</v>
+      </c>
+      <c r="U35">
+        <v>3622</v>
+      </c>
+      <c r="V35">
+        <v>2126</v>
+      </c>
+      <c r="W35">
+        <v>2753</v>
+      </c>
+      <c r="X35">
+        <v>3753</v>
+      </c>
+      <c r="Y35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>9</v>
+      </c>
+      <c r="Q36">
+        <v>173</v>
+      </c>
+      <c r="R36">
+        <v>306</v>
+      </c>
+      <c r="S36">
+        <v>73</v>
+      </c>
+      <c r="T36">
+        <v>276</v>
+      </c>
+      <c r="U36">
+        <v>178</v>
+      </c>
+      <c r="V36">
+        <v>68</v>
+      </c>
+      <c r="W36">
+        <v>51</v>
+      </c>
+      <c r="X36">
+        <v>101</v>
+      </c>
+      <c r="Y36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37">
+        <v>44</v>
+      </c>
+      <c r="C37">
+        <v>44</v>
+      </c>
+      <c r="D37">
+        <v>44</v>
+      </c>
+      <c r="E37">
+        <v>44</v>
+      </c>
+      <c r="F37">
+        <v>44</v>
+      </c>
+      <c r="G37">
+        <v>44</v>
+      </c>
+      <c r="H37">
+        <v>44</v>
+      </c>
+      <c r="I37">
+        <v>44</v>
+      </c>
+      <c r="J37">
+        <v>44</v>
+      </c>
+      <c r="K37">
+        <v>44</v>
+      </c>
+      <c r="L37">
+        <v>44</v>
+      </c>
+      <c r="M37">
+        <v>44</v>
+      </c>
+      <c r="N37">
+        <v>26</v>
+      </c>
+      <c r="O37">
+        <v>80</v>
+      </c>
+      <c r="P37">
+        <v>243</v>
+      </c>
+      <c r="Q37">
+        <v>1311</v>
+      </c>
+      <c r="R37">
+        <v>3107</v>
+      </c>
+      <c r="S37">
+        <v>8962</v>
+      </c>
+      <c r="T37">
+        <v>4928</v>
+      </c>
+      <c r="U37">
+        <v>13120</v>
+      </c>
+      <c r="V37">
+        <v>6766</v>
+      </c>
+      <c r="W37">
+        <v>8488</v>
+      </c>
+      <c r="X37">
+        <v>10238</v>
+      </c>
+      <c r="Y37">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38">
+        <v>169</v>
+      </c>
+      <c r="C38">
+        <v>169</v>
+      </c>
+      <c r="D38">
+        <v>169</v>
+      </c>
+      <c r="E38">
+        <v>169</v>
+      </c>
+      <c r="F38">
+        <v>169</v>
+      </c>
+      <c r="G38">
+        <v>169</v>
+      </c>
+      <c r="H38">
+        <v>169</v>
+      </c>
+      <c r="I38">
+        <v>169</v>
+      </c>
+      <c r="J38">
+        <v>169</v>
+      </c>
+      <c r="K38">
+        <v>169</v>
+      </c>
+      <c r="L38">
+        <v>169</v>
+      </c>
+      <c r="M38">
+        <v>169</v>
+      </c>
+      <c r="N38">
+        <v>50</v>
+      </c>
+      <c r="O38">
+        <v>28</v>
+      </c>
+      <c r="P38">
+        <v>162</v>
+      </c>
+      <c r="Q38">
+        <v>6982</v>
+      </c>
+      <c r="R38">
+        <v>4405</v>
+      </c>
+      <c r="S38">
+        <v>7632</v>
+      </c>
+      <c r="T38">
+        <v>4486</v>
+      </c>
+      <c r="U38">
+        <v>7472</v>
+      </c>
+      <c r="V38">
+        <v>6695</v>
+      </c>
+      <c r="W38">
+        <v>6734</v>
+      </c>
+      <c r="X38">
+        <v>10048</v>
+      </c>
+      <c r="Y38">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39">
+        <v>124</v>
+      </c>
+      <c r="C39">
+        <v>122</v>
+      </c>
+      <c r="D39">
+        <v>119</v>
+      </c>
+      <c r="E39">
+        <v>115</v>
+      </c>
+      <c r="F39">
+        <v>108</v>
+      </c>
+      <c r="G39">
+        <v>105</v>
+      </c>
+      <c r="H39">
+        <v>99</v>
+      </c>
+      <c r="I39">
+        <v>89</v>
+      </c>
+      <c r="J39">
+        <v>77</v>
+      </c>
+      <c r="K39">
+        <v>61</v>
+      </c>
+      <c r="L39">
+        <v>44</v>
+      </c>
+      <c r="M39">
+        <v>25</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+      <c r="O39">
+        <v>4</v>
+      </c>
+      <c r="P39">
+        <v>32</v>
+      </c>
+      <c r="Q39">
+        <v>822</v>
+      </c>
+      <c r="R39">
+        <v>1270</v>
+      </c>
+      <c r="S39">
+        <v>5411</v>
+      </c>
+      <c r="T39">
+        <v>2437</v>
+      </c>
+      <c r="U39">
+        <v>5112</v>
+      </c>
+      <c r="V39">
+        <v>2255</v>
+      </c>
+      <c r="W39">
+        <v>3082</v>
+      </c>
+      <c r="X39">
+        <v>3645</v>
+      </c>
+      <c r="Y39">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>21</v>
+      </c>
+      <c r="P40">
+        <v>28</v>
+      </c>
+      <c r="Q40">
+        <v>87</v>
+      </c>
+      <c r="R40">
+        <v>88</v>
+      </c>
+      <c r="S40">
+        <v>219</v>
+      </c>
+      <c r="T40">
+        <v>172</v>
+      </c>
+      <c r="U40">
+        <v>312</v>
+      </c>
+      <c r="V40">
+        <v>256</v>
+      </c>
+      <c r="W40">
+        <v>182</v>
+      </c>
+      <c r="X40">
+        <v>62</v>
+      </c>
+      <c r="Y40">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41">
+        <v>2097</v>
+      </c>
+      <c r="C41">
+        <v>2130</v>
+      </c>
+      <c r="D41">
+        <v>2174</v>
+      </c>
+      <c r="E41">
+        <v>2231</v>
+      </c>
+      <c r="F41">
+        <v>2348</v>
+      </c>
+      <c r="G41">
+        <v>2397</v>
+      </c>
+      <c r="H41">
+        <v>2499</v>
+      </c>
+      <c r="I41">
+        <v>2667</v>
+      </c>
+      <c r="J41">
+        <v>2906</v>
+      </c>
+      <c r="K41">
+        <v>3222</v>
+      </c>
+      <c r="L41">
+        <v>3628</v>
+      </c>
+      <c r="M41">
+        <v>4030</v>
+      </c>
+      <c r="N41">
+        <v>5564</v>
+      </c>
+      <c r="O41">
+        <v>840</v>
+      </c>
+      <c r="P41">
+        <v>4073</v>
+      </c>
+      <c r="Q41">
+        <v>2620</v>
+      </c>
+      <c r="R41">
+        <v>1568</v>
+      </c>
+      <c r="S41">
+        <v>3705</v>
+      </c>
+      <c r="T41">
+        <v>5479</v>
+      </c>
+      <c r="U41">
+        <v>2793</v>
+      </c>
+      <c r="V41">
+        <v>1422</v>
+      </c>
+      <c r="W41">
+        <v>1610</v>
+      </c>
+      <c r="X41">
+        <v>2413</v>
+      </c>
+      <c r="Y41">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42">
+        <v>2834</v>
+      </c>
+      <c r="C42">
+        <v>2834</v>
+      </c>
+      <c r="D42">
+        <v>2834</v>
+      </c>
+      <c r="E42">
+        <v>2834</v>
+      </c>
+      <c r="F42">
+        <v>2834</v>
+      </c>
+      <c r="G42">
+        <v>2834</v>
+      </c>
+      <c r="H42">
+        <v>2834</v>
+      </c>
+      <c r="I42">
+        <v>2834</v>
+      </c>
+      <c r="J42">
+        <v>2834</v>
+      </c>
+      <c r="K42">
+        <v>2834</v>
+      </c>
+      <c r="L42">
+        <v>2834</v>
+      </c>
+      <c r="M42">
+        <v>2834</v>
+      </c>
+      <c r="N42">
+        <v>2317</v>
+      </c>
+      <c r="O42">
+        <v>421</v>
+      </c>
+      <c r="P42">
+        <v>616</v>
+      </c>
+      <c r="Q42">
+        <v>417</v>
+      </c>
+      <c r="R42">
+        <v>981</v>
+      </c>
+      <c r="S42">
+        <v>3284</v>
+      </c>
+      <c r="T42">
+        <v>5143</v>
+      </c>
+      <c r="U42">
+        <v>2629</v>
+      </c>
+      <c r="V42">
+        <v>820</v>
+      </c>
+      <c r="W42">
+        <v>1083</v>
+      </c>
+      <c r="X42">
+        <v>1744</v>
+      </c>
+      <c r="Y42">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>5</v>
+      </c>
+      <c r="Q43">
+        <v>800</v>
+      </c>
+      <c r="R43">
+        <v>1021</v>
+      </c>
+      <c r="S43">
+        <v>319</v>
+      </c>
+      <c r="T43">
+        <v>284</v>
+      </c>
+      <c r="U43">
+        <v>473</v>
+      </c>
+      <c r="V43">
+        <v>959</v>
+      </c>
+      <c r="W43">
+        <v>880</v>
+      </c>
+      <c r="X43">
+        <v>2071</v>
+      </c>
+      <c r="Y43">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>483</v>
+      </c>
+      <c r="R44">
+        <v>315</v>
+      </c>
+      <c r="S44">
+        <v>46</v>
+      </c>
+      <c r="T44">
+        <v>76</v>
+      </c>
+      <c r="U44">
+        <v>61</v>
+      </c>
+      <c r="V44">
+        <v>24</v>
+      </c>
+      <c r="W44">
+        <v>11</v>
+      </c>
+      <c r="X44">
+        <v>2</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>117</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>83</v>
+      </c>
+      <c r="R45">
+        <v>12</v>
+      </c>
+      <c r="S45">
+        <v>79</v>
+      </c>
+      <c r="T45">
+        <v>14</v>
+      </c>
+      <c r="U45">
+        <v>10</v>
+      </c>
+      <c r="V45">
+        <v>29</v>
+      </c>
+      <c r="W45">
+        <v>38</v>
+      </c>
+      <c r="X45">
+        <v>64</v>
+      </c>
+      <c r="Y45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>202</v>
+      </c>
+      <c r="Q46">
+        <v>711</v>
+      </c>
+      <c r="R46">
+        <v>2527</v>
+      </c>
+      <c r="S46">
+        <v>701</v>
+      </c>
+      <c r="T46">
+        <v>648</v>
+      </c>
+      <c r="U46">
+        <v>977</v>
+      </c>
+      <c r="V46">
+        <v>447</v>
+      </c>
+      <c r="W46">
+        <v>540</v>
+      </c>
+      <c r="X46">
+        <v>968</v>
+      </c>
+      <c r="Y46">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>4</v>
+      </c>
+      <c r="P47">
+        <v>59</v>
+      </c>
+      <c r="Q47">
+        <v>521</v>
+      </c>
+      <c r="R47">
+        <v>937</v>
+      </c>
+      <c r="S47">
+        <v>186</v>
+      </c>
+      <c r="T47">
+        <v>103</v>
+      </c>
+      <c r="U47">
+        <v>122</v>
+      </c>
+      <c r="V47">
+        <v>48</v>
+      </c>
+      <c r="W47">
+        <v>69</v>
+      </c>
+      <c r="X47">
+        <v>125</v>
+      </c>
+      <c r="Y47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>98</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>22</v>
+      </c>
+      <c r="R48">
+        <v>7</v>
+      </c>
+      <c r="S48">
+        <v>4</v>
+      </c>
+      <c r="T48">
+        <v>6</v>
+      </c>
+      <c r="U48">
+        <v>3</v>
+      </c>
+      <c r="V48">
+        <v>57</v>
+      </c>
+      <c r="W48">
+        <v>114</v>
+      </c>
+      <c r="X48">
+        <v>83</v>
+      </c>
+      <c r="Y48">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>10</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>147</v>
+      </c>
+      <c r="R49">
+        <v>314</v>
+      </c>
+      <c r="S49">
+        <v>156</v>
+      </c>
+      <c r="T49">
+        <v>1064</v>
+      </c>
+      <c r="U49">
+        <v>1295</v>
+      </c>
+      <c r="V49">
+        <v>522</v>
+      </c>
+      <c r="W49">
+        <v>175</v>
+      </c>
+      <c r="X49">
+        <v>366</v>
+      </c>
+      <c r="Y49">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>16</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>18</v>
+      </c>
+      <c r="U50">
+        <v>180</v>
+      </c>
+      <c r="V50">
+        <v>12</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>10</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="53" spans="1:25" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A53" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B53" s="3">
+        <f>SUM(B2:B51)</f>
+        <v>26186</v>
+      </c>
+      <c r="C53" s="3">
+        <f>SUM(C2:C51)</f>
+        <v>26322</v>
+      </c>
+      <c r="D53" s="3">
+        <f>SUM(D2:D51)</f>
+        <v>26510</v>
+      </c>
+      <c r="E53" s="3">
+        <f>SUM(E2:E51)</f>
+        <v>26766</v>
+      </c>
+      <c r="F53" s="3">
+        <f>SUM(F2:F51)</f>
+        <v>27301</v>
+      </c>
+      <c r="G53" s="3">
+        <f>SUM(G2:G51)</f>
+        <v>27603</v>
+      </c>
+      <c r="H53" s="3">
+        <f>SUM(H2:H51)</f>
+        <v>28236</v>
+      </c>
+      <c r="I53" s="3">
+        <f>SUM(I2:I51)</f>
+        <v>29277</v>
+      </c>
+      <c r="J53" s="3">
+        <f>SUM(J2:J51)</f>
+        <v>30894</v>
+      </c>
+      <c r="K53" s="3">
+        <f>SUM(K2:K51)</f>
+        <v>33280</v>
+      </c>
+      <c r="L53" s="3">
+        <f>SUM(L2:L51)</f>
+        <v>37339</v>
+      </c>
+      <c r="M53" s="3">
+        <f>SUM(M2:M51)</f>
+        <v>44236</v>
+      </c>
+      <c r="N53" s="3">
+        <f>SUM(N2:N51)</f>
+        <v>53350</v>
+      </c>
+      <c r="O53" s="3">
+        <f>SUM(O2:O51)</f>
+        <v>55776</v>
+      </c>
+      <c r="P53" s="3">
+        <f>SUM(P2:P51)</f>
+        <v>101995</v>
+      </c>
+      <c r="Q53" s="3">
+        <f>SUM(Q2:Q51)</f>
+        <v>186166</v>
+      </c>
+      <c r="R53" s="3">
+        <f>SUM(R2:R51)</f>
+        <v>81015</v>
+      </c>
+      <c r="S53" s="3">
+        <f>SUM(S2:S51)</f>
+        <v>143699</v>
+      </c>
+      <c r="T53" s="3">
+        <f>SUM(T2:T51)</f>
+        <v>162805</v>
+      </c>
+      <c r="U53" s="3">
+        <f>SUM(U2:U51)</f>
+        <v>164639</v>
+      </c>
+      <c r="V53" s="3">
+        <f>SUM(V2:V51)</f>
+        <v>86334</v>
+      </c>
+      <c r="W53" s="3">
+        <f>SUM(W2:W51)</f>
+        <v>80499</v>
+      </c>
+      <c r="X53" s="3">
+        <f>SUM(X2:X51)</f>
+        <v>83721</v>
+      </c>
+      <c r="Y53" s="3">
+        <f>SUM(Y2:Y51)</f>
+        <v>29895</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AF76409-3B5B-4850-BA78-EE1975F668B1}">
+  <dimension ref="A1:AG59"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="19.9453125" customWidth="1"/>
+    <col min="10" max="10" width="13.41796875" customWidth="1"/>
+    <col min="11" max="11" width="10.47265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="J1" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="K1" s="35"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="W1" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="27">
+        <v>1894</v>
+      </c>
+      <c r="C2" s="27">
+        <v>1895</v>
+      </c>
+      <c r="D2" s="27">
+        <v>1896</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="30">
+        <v>18.940000000000001</v>
+      </c>
+      <c r="G2" s="30">
+        <v>18.95</v>
+      </c>
+      <c r="H2" s="30">
+        <v>18.96</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="M2" s="27">
+        <v>1893</v>
+      </c>
+      <c r="N2" s="27">
+        <v>1894</v>
+      </c>
+      <c r="O2" s="27">
+        <v>1895</v>
+      </c>
+      <c r="P2" s="27">
+        <v>1896</v>
+      </c>
+      <c r="R2" s="30">
+        <v>18.93</v>
+      </c>
+      <c r="S2" s="30">
+        <v>18.940000000000001</v>
+      </c>
+      <c r="T2" s="30">
+        <v>18.95</v>
+      </c>
+      <c r="U2" s="30">
+        <v>18.96</v>
+      </c>
+      <c r="W2" s="31">
+        <v>1896</v>
+      </c>
+      <c r="X2" s="31">
+        <v>1897</v>
+      </c>
+      <c r="Y2" s="31">
+        <v>1898</v>
+      </c>
+      <c r="Z2" s="31">
+        <v>1899</v>
+      </c>
+      <c r="AA2" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="AC2" s="32">
+        <v>18.96</v>
+      </c>
+      <c r="AD2" s="32">
+        <v>18.97</v>
+      </c>
+      <c r="AE2" s="32">
+        <v>18.98</v>
+      </c>
+      <c r="AF2" s="32">
+        <v>18.989999999999998</v>
+      </c>
+      <c r="AG2" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2474</v>
+      </c>
+      <c r="C3" s="3">
+        <v>21855</v>
+      </c>
+      <c r="D3" s="3">
+        <v>43592</v>
+      </c>
+      <c r="F3" s="29">
+        <f t="shared" ref="F3:H5" si="0">B3/B$15 * 100</f>
+        <v>34.213801687180194</v>
+      </c>
+      <c r="G3" s="29">
+        <f t="shared" si="0"/>
+        <v>25.57815645334956</v>
+      </c>
+      <c r="H3" s="29">
+        <f t="shared" si="0"/>
+        <v>24.616010119262739</v>
+      </c>
+      <c r="J3" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K3" s="29">
+        <f>J3/J$15*100</f>
+        <v>1.2228676245796393</v>
+      </c>
+      <c r="M3">
+        <v>1000</v>
+      </c>
+      <c r="N3">
+        <v>4450</v>
+      </c>
+      <c r="O3">
+        <v>10950</v>
+      </c>
+      <c r="P3">
+        <v>18400</v>
+      </c>
+      <c r="R3" s="29">
+        <f>M3/M$15*100</f>
+        <v>19.801980198019802</v>
+      </c>
+      <c r="S3" s="29">
+        <f>N3/N$15*100</f>
+        <v>33.208955223880601</v>
+      </c>
+      <c r="T3" s="29">
+        <f>O3/O$15*100</f>
+        <v>28.853754940711461</v>
+      </c>
+      <c r="U3" s="29">
+        <f>P3/P$15*100</f>
+        <v>30.898404701931149</v>
+      </c>
+      <c r="W3" s="3">
+        <v>46434</v>
+      </c>
+      <c r="X3" s="3">
+        <v>17774</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>24586</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>32090</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>120884</v>
+      </c>
+      <c r="AC3" s="29">
+        <f>W3/W$15*100</f>
+        <v>24.418127701643861</v>
+      </c>
+      <c r="AD3" s="29">
+        <f t="shared" ref="AD3:AG13" si="1">X3/X$15*100</f>
+        <v>21.254409566517189</v>
+      </c>
+      <c r="AE3" s="29">
+        <f t="shared" si="1"/>
+        <v>12.493267071150543</v>
+      </c>
+      <c r="AF3" s="29">
+        <f t="shared" si="1"/>
+        <v>15.152731410870867</v>
+      </c>
+      <c r="AG3" s="29">
+        <f t="shared" si="1"/>
+        <v>17.715627280694299</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="3">
+        <v>314</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1515</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1911</v>
+      </c>
+      <c r="F4" s="29">
+        <f t="shared" si="0"/>
+        <v>4.3424146037892406</v>
+      </c>
+      <c r="G4" s="29">
+        <f t="shared" si="0"/>
+        <v>1.7730911474181921</v>
+      </c>
+      <c r="H4" s="29">
+        <f t="shared" si="0"/>
+        <v>1.079124503071919</v>
+      </c>
+      <c r="J4" s="3">
+        <v>16000</v>
+      </c>
+      <c r="K4" s="29">
+        <f>J4/J$15*100</f>
+        <v>4.8914704983185571</v>
+      </c>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="W4" s="3">
+        <v>1954</v>
+      </c>
+      <c r="X4" s="3">
+        <v>1344</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>4034</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>1540</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>8872</v>
+      </c>
+      <c r="AC4" s="29">
+        <f t="shared" ref="AC4:AC13" si="2">W4/W$15*100</f>
+        <v>1.0275449353708943</v>
+      </c>
+      <c r="AD4" s="29">
+        <f t="shared" si="1"/>
+        <v>1.6071748878923768</v>
+      </c>
+      <c r="AE4" s="29">
+        <f t="shared" si="1"/>
+        <v>2.0498592436761283</v>
+      </c>
+      <c r="AF4" s="29">
+        <f t="shared" si="1"/>
+        <v>0.72718000538302074</v>
+      </c>
+      <c r="AG4" s="29">
+        <f t="shared" si="1"/>
+        <v>1.3001972571582658</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="3">
+        <v>128</v>
+      </c>
+      <c r="C5" s="3">
+        <v>6452</v>
+      </c>
+      <c r="D5" s="3">
+        <v>19213</v>
+      </c>
+      <c r="F5" s="29">
+        <f t="shared" si="0"/>
+        <v>1.770156271608353</v>
+      </c>
+      <c r="G5" s="29">
+        <f t="shared" si="0"/>
+        <v>7.5511446093347683</v>
+      </c>
+      <c r="H5" s="29">
+        <f t="shared" si="0"/>
+        <v>10.849408203830864</v>
+      </c>
+      <c r="J5" s="3">
+        <v>25000</v>
+      </c>
+      <c r="K5" s="29">
+        <f>J5/J$15*100</f>
+        <v>7.6429226536227457</v>
+      </c>
+      <c r="M5">
+        <v>950</v>
+      </c>
+      <c r="N5">
+        <v>1700</v>
+      </c>
+      <c r="O5">
+        <v>3700</v>
+      </c>
+      <c r="P5">
+        <v>7900</v>
+      </c>
+      <c r="R5" s="29">
+        <f>M5/M$15*100</f>
+        <v>18.811881188118811</v>
+      </c>
+      <c r="S5" s="29">
+        <f>N5/N$15*100</f>
+        <v>12.686567164179104</v>
+      </c>
+      <c r="T5" s="29">
+        <f>O5/O$15*100</f>
+        <v>9.749670619235836</v>
+      </c>
+      <c r="U5" s="29">
+        <f>P5/P$15*100</f>
+        <v>13.266162888329136</v>
+      </c>
+      <c r="W5" s="3">
+        <v>20195</v>
+      </c>
+      <c r="X5" s="3">
+        <v>6710</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>28190</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>26399</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>81494</v>
+      </c>
+      <c r="AC5" s="29">
+        <f t="shared" si="2"/>
+        <v>10.619892512699698</v>
+      </c>
+      <c r="AD5" s="29">
+        <f t="shared" si="1"/>
+        <v>8.0239162929745902</v>
+      </c>
+      <c r="AE5" s="29">
+        <f t="shared" si="1"/>
+        <v>14.324623718202792</v>
+      </c>
+      <c r="AF5" s="29">
+        <f t="shared" si="1"/>
+        <v>12.465470754614524</v>
+      </c>
+      <c r="AG5" s="29">
+        <f t="shared" si="1"/>
+        <v>11.942997663982837</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="W6">
+        <v>3</v>
+      </c>
+      <c r="X6">
+        <v>25</v>
+      </c>
+      <c r="Y6">
+        <v>189</v>
+      </c>
+      <c r="Z6">
+        <v>590</v>
+      </c>
+      <c r="AA6">
+        <v>807</v>
+      </c>
+      <c r="AC6" s="29">
+        <f t="shared" si="2"/>
+        <v>1.5776022549194898E-3</v>
+      </c>
+      <c r="AD6" s="29">
+        <f t="shared" si="1"/>
+        <v>2.9895366218236175E-2</v>
+      </c>
+      <c r="AE6" s="29">
+        <f t="shared" si="1"/>
+        <v>9.6039513399798784E-2</v>
+      </c>
+      <c r="AF6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.27859493712726124</v>
+      </c>
+      <c r="AG6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.11826636457695228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>119</v>
+      </c>
+      <c r="F7" s="29">
+        <f t="shared" ref="F7:H9" si="3">B7/B$15 * 100</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="29">
+        <f t="shared" si="3"/>
+        <v>2.9258929825382706E-2</v>
+      </c>
+      <c r="H7" s="29">
+        <f t="shared" si="3"/>
+        <v>6.7198229129020598E-2</v>
+      </c>
+      <c r="J7" s="3">
+        <v>600</v>
+      </c>
+      <c r="K7" s="29">
+        <f>J7/J$15*100</f>
+        <v>0.18343014368694588</v>
+      </c>
+      <c r="P7">
+        <v>50</v>
+      </c>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29">
+        <f>P7/P$15*100</f>
+        <v>8.3963056255247692E-2</v>
+      </c>
+      <c r="W7">
+        <v>176</v>
+      </c>
+      <c r="X7">
+        <v>327</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>4031</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>5379</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>9913</v>
+      </c>
+      <c r="AC7" s="29">
+        <f t="shared" si="2"/>
+        <v>9.2552665621943392E-2</v>
+      </c>
+      <c r="AD7" s="29">
+        <f t="shared" si="1"/>
+        <v>0.39103139013452914</v>
+      </c>
+      <c r="AE7" s="29">
+        <f t="shared" si="1"/>
+        <v>2.0483348069554963</v>
+      </c>
+      <c r="AF7" s="29">
+        <f t="shared" si="1"/>
+        <v>2.5399358759449799</v>
+      </c>
+      <c r="AG7" s="29">
+        <f t="shared" si="1"/>
+        <v>1.4527564709434051</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="3">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3">
+        <v>54</v>
+      </c>
+      <c r="F8" s="29">
+        <f t="shared" si="3"/>
+        <v>0.13829345871940257</v>
+      </c>
+      <c r="G8" s="29">
+        <f t="shared" si="3"/>
+        <v>8.192500351107157E-2</v>
+      </c>
+      <c r="H8" s="29">
+        <f t="shared" si="3"/>
+        <v>3.0493314058547161E-2</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="29">
+        <f>J8/J$15*100</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="29"/>
+      <c r="W8">
+        <v>56</v>
+      </c>
+      <c r="X8">
+        <v>100</v>
+      </c>
+      <c r="Y8">
+        <v>537</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>1058</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>1751</v>
+      </c>
+      <c r="AC8" s="29">
+        <f t="shared" si="2"/>
+        <v>2.9448575425163808E-2</v>
+      </c>
+      <c r="AD8" s="29">
+        <f t="shared" si="1"/>
+        <v>0.1195814648729447</v>
+      </c>
+      <c r="AE8" s="29">
+        <f t="shared" si="1"/>
+        <v>0.27287417299307903</v>
+      </c>
+      <c r="AF8" s="29">
+        <f t="shared" si="1"/>
+        <v>0.49958210759430915</v>
+      </c>
+      <c r="AG8" s="29">
+        <f t="shared" si="1"/>
+        <v>0.25661016651083451</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="3">
+        <v>185</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1796</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1455</v>
+      </c>
+      <c r="F9" s="29">
+        <f t="shared" si="3"/>
+        <v>2.5584289863089476</v>
+      </c>
+      <c r="G9" s="29">
+        <f t="shared" si="3"/>
+        <v>2.1019615186554939</v>
+      </c>
+      <c r="H9" s="29">
+        <f t="shared" si="3"/>
+        <v>0.8216254065775207</v>
+      </c>
+      <c r="J9" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K9" s="29">
+        <f>J9/J$15*100</f>
+        <v>3.3628859675940079</v>
+      </c>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="29"/>
+      <c r="W9" s="3">
+        <v>1602</v>
+      </c>
+      <c r="X9">
+        <v>424</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>1384</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>4333</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>7743</v>
+      </c>
+      <c r="AC9" s="29">
+        <f t="shared" si="2"/>
+        <v>0.84243960412700747</v>
+      </c>
+      <c r="AD9" s="29">
+        <f t="shared" si="1"/>
+        <v>0.50702541106128551</v>
+      </c>
+      <c r="AE9" s="29">
+        <f t="shared" si="1"/>
+        <v>0.7032734737847699</v>
+      </c>
+      <c r="AF9" s="29">
+        <f t="shared" si="1"/>
+        <v>2.0460201060549541</v>
+      </c>
+      <c r="AG9" s="29">
+        <f t="shared" si="1"/>
+        <v>1.1347415872606463</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="U10" s="29"/>
+      <c r="W10">
+        <v>99</v>
+      </c>
+      <c r="X10">
+        <v>140</v>
+      </c>
+      <c r="Y10">
+        <v>212</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>1016</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>1467</v>
+      </c>
+      <c r="AC10" s="29">
+        <f t="shared" si="2"/>
+        <v>5.206087441234316E-2</v>
+      </c>
+      <c r="AD10" s="29">
+        <f t="shared" si="1"/>
+        <v>0.16741405082212257</v>
+      </c>
+      <c r="AE10" s="29">
+        <f t="shared" si="1"/>
+        <v>0.10772686159130868</v>
+      </c>
+      <c r="AF10" s="29">
+        <f t="shared" si="1"/>
+        <v>0.47974992562931762</v>
+      </c>
+      <c r="AG10" s="29">
+        <f t="shared" si="1"/>
+        <v>0.21498978542055636</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="3">
+        <v>328</v>
+      </c>
+      <c r="C11" s="3">
+        <v>21266</v>
+      </c>
+      <c r="D11" s="3">
+        <v>41495</v>
+      </c>
+      <c r="F11" s="29">
+        <f t="shared" ref="F11:H13" si="4">B11/B$15 * 100</f>
+        <v>4.5360254459964038</v>
+      </c>
+      <c r="G11" s="29">
+        <f t="shared" si="4"/>
+        <v>24.888816066663548</v>
+      </c>
+      <c r="H11" s="29">
+        <f t="shared" si="4"/>
+        <v>23.431853089989158</v>
+      </c>
+      <c r="J11" s="3">
+        <v>26000</v>
+      </c>
+      <c r="K11" s="29">
+        <f>J11/J$15*100</f>
+        <v>7.9486395597676545</v>
+      </c>
+      <c r="M11">
+        <v>2300</v>
+      </c>
+      <c r="N11">
+        <v>2300</v>
+      </c>
+      <c r="O11">
+        <v>14900</v>
+      </c>
+      <c r="P11">
+        <v>23100</v>
+      </c>
+      <c r="R11" s="29">
+        <f t="shared" ref="R11:U12" si="5">M11/M$15*100</f>
+        <v>45.544554455445549</v>
+      </c>
+      <c r="S11" s="29">
+        <f t="shared" si="5"/>
+        <v>17.164179104477611</v>
+      </c>
+      <c r="T11" s="29">
+        <f t="shared" si="5"/>
+        <v>39.26218708827404</v>
+      </c>
+      <c r="U11" s="29">
+        <f t="shared" si="5"/>
+        <v>38.790931989924431</v>
+      </c>
+      <c r="W11" s="3">
+        <v>44119</v>
+      </c>
+      <c r="X11" s="3">
+        <v>19649</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>26209</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>12698</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>102675</v>
+      </c>
+      <c r="AC11" s="29">
+        <f t="shared" si="2"/>
+        <v>23.200744628264321</v>
+      </c>
+      <c r="AD11" s="29">
+        <f t="shared" si="1"/>
+        <v>23.496562032884903</v>
+      </c>
+      <c r="AE11" s="29">
+        <f t="shared" si="1"/>
+        <v>13.317987337012308</v>
+      </c>
+      <c r="AF11" s="29">
+        <f t="shared" si="1"/>
+        <v>5.9959296807490894</v>
+      </c>
+      <c r="AG11" s="29">
+        <f t="shared" si="1"/>
+        <v>15.047086719874317</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="3">
+        <v>3641</v>
+      </c>
+      <c r="C12" s="3">
+        <v>32417</v>
+      </c>
+      <c r="D12" s="3">
+        <v>69078</v>
+      </c>
+      <c r="F12" s="29">
+        <f t="shared" si="4"/>
+        <v>50.35264831973447</v>
+      </c>
+      <c r="G12" s="29">
+        <f t="shared" si="4"/>
+        <v>37.939469125977247</v>
+      </c>
+      <c r="H12" s="29">
+        <f t="shared" si="4"/>
+        <v>39.007724972894827</v>
+      </c>
+      <c r="J12" s="3">
+        <v>244500</v>
+      </c>
+      <c r="K12" s="29">
+        <f>J12/J$15*100</f>
+        <v>74.747783552430448</v>
+      </c>
+      <c r="M12">
+        <v>800</v>
+      </c>
+      <c r="N12">
+        <v>4950</v>
+      </c>
+      <c r="O12">
+        <v>8400</v>
+      </c>
+      <c r="P12">
+        <v>10100</v>
+      </c>
+      <c r="R12" s="29">
+        <f t="shared" si="5"/>
+        <v>15.841584158415841</v>
+      </c>
+      <c r="S12" s="29">
+        <f t="shared" si="5"/>
+        <v>36.940298507462686</v>
+      </c>
+      <c r="T12" s="29">
+        <f t="shared" si="5"/>
+        <v>22.134387351778656</v>
+      </c>
+      <c r="U12" s="29">
+        <f t="shared" si="5"/>
+        <v>16.960537363560032</v>
+      </c>
+      <c r="W12" s="3">
+        <v>75419</v>
+      </c>
+      <c r="X12" s="3">
+        <v>36654</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>105862</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>122006</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>339941</v>
+      </c>
+      <c r="AC12" s="29">
+        <f t="shared" si="2"/>
+        <v>39.660394821257668</v>
+      </c>
+      <c r="AD12" s="29">
+        <f t="shared" si="1"/>
+        <v>43.831390134529144</v>
+      </c>
+      <c r="AE12" s="29">
+        <f t="shared" si="1"/>
+        <v>53.793306706505284</v>
+      </c>
+      <c r="AF12" s="29">
+        <f t="shared" si="1"/>
+        <v>57.610599829065478</v>
+      </c>
+      <c r="AG12" s="29">
+        <f t="shared" si="1"/>
+        <v>49.818570310599419</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="3">
+        <v>151</v>
+      </c>
+      <c r="C13" s="3">
+        <v>48</v>
+      </c>
+      <c r="D13" s="3">
+        <v>171</v>
+      </c>
+      <c r="F13" s="29">
+        <f t="shared" si="4"/>
+        <v>2.0882312266629786</v>
+      </c>
+      <c r="G13" s="29">
+        <f t="shared" si="4"/>
+        <v>5.6177145264734794E-2</v>
+      </c>
+      <c r="H13" s="29">
+        <f t="shared" si="4"/>
+        <v>9.6562161185399356E-2</v>
+      </c>
+      <c r="K13" s="29">
+        <f>J13/J$15*100</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="29"/>
+      <c r="W13">
+        <v>105</v>
+      </c>
+      <c r="X13">
+        <v>478</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>1560</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>4668</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>6811</v>
+      </c>
+      <c r="AC13" s="29">
+        <f t="shared" si="2"/>
+        <v>5.5216078922182138E-2</v>
+      </c>
+      <c r="AD13" s="29">
+        <f t="shared" si="1"/>
+        <v>0.57159940209267568</v>
+      </c>
+      <c r="AE13" s="29">
+        <f t="shared" si="1"/>
+        <v>0.79270709472849776</v>
+      </c>
+      <c r="AF13" s="29">
+        <f t="shared" si="1"/>
+        <v>2.2042053669661956</v>
+      </c>
+      <c r="AG13" s="29">
+        <f t="shared" si="1"/>
+        <v>0.99815639297846581</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
+        <f>SUM(B3:B13)</f>
+        <v>7231</v>
+      </c>
+      <c r="C15" s="3">
+        <f>SUM(C3:C13)</f>
+        <v>85444</v>
+      </c>
+      <c r="D15" s="3">
+        <f>SUM(D3:D13)</f>
+        <v>177088</v>
+      </c>
+      <c r="F15" s="3">
+        <f>SUM(F3:F13)</f>
+        <v>99.999999999999986</v>
+      </c>
+      <c r="G15" s="3">
+        <f>SUM(G3:G13)</f>
+        <v>100</v>
+      </c>
+      <c r="H15" s="3">
+        <f>SUM(H3:H13)</f>
+        <v>100</v>
+      </c>
+      <c r="J15" s="3">
+        <f>SUM(J3:J13)</f>
+        <v>327100</v>
+      </c>
+      <c r="K15" s="3">
+        <f>SUM(K3:K13)</f>
+        <v>100</v>
+      </c>
+      <c r="M15" s="3">
+        <f t="shared" ref="M15:AG15" si="6">SUM(M3:M13)</f>
+        <v>5050</v>
+      </c>
+      <c r="N15" s="3">
+        <f t="shared" si="6"/>
+        <v>13400</v>
+      </c>
+      <c r="O15" s="3">
+        <f t="shared" si="6"/>
+        <v>37950</v>
+      </c>
+      <c r="P15" s="3">
+        <f t="shared" si="6"/>
+        <v>59550</v>
+      </c>
+      <c r="R15" s="3">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="S15" s="3">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="T15" s="3">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="U15" s="3">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="W15" s="3">
+        <f t="shared" si="6"/>
+        <v>190162</v>
+      </c>
+      <c r="X15" s="3">
+        <f t="shared" si="6"/>
+        <v>83625</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="6"/>
+        <v>196794</v>
+      </c>
+      <c r="Z15" s="3">
+        <f t="shared" si="6"/>
+        <v>211777</v>
+      </c>
+      <c r="AA15" s="3">
+        <f t="shared" si="6"/>
+        <v>682358</v>
+      </c>
+      <c r="AC15" s="3">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="AD15" s="3">
+        <f t="shared" si="6"/>
+        <v>99.999999999999986</v>
+      </c>
+      <c r="AE15" s="3">
+        <f t="shared" si="6"/>
+        <v>100.00000000000001</v>
+      </c>
+      <c r="AF15" s="3">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="AG15" s="3">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30">
+        <v>1884</v>
+      </c>
+      <c r="C30" s="3">
+        <v>11905</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31">
+        <f>B30+1</f>
+        <v>1885</v>
+      </c>
+      <c r="C31" s="3">
+        <v>17054</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32">
+        <f t="shared" ref="B32:B44" si="7">B31+1</f>
+        <v>1886</v>
+      </c>
+      <c r="C32" s="3">
+        <v>16279</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33">
+        <f t="shared" si="7"/>
+        <v>1887</v>
+      </c>
+      <c r="C33" s="3">
+        <v>15970</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34">
+        <f t="shared" si="7"/>
+        <v>1888</v>
+      </c>
+      <c r="C34" s="3">
+        <v>18031</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35">
+        <f t="shared" si="7"/>
+        <v>1889</v>
+      </c>
+      <c r="C35" s="3">
+        <v>17215</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36">
+        <f t="shared" si="7"/>
+        <v>1890</v>
+      </c>
+      <c r="C36" s="3">
+        <v>31345</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37">
+        <f t="shared" si="7"/>
+        <v>1891</v>
+      </c>
+      <c r="C37" s="3">
+        <v>28557</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38">
+        <f t="shared" si="7"/>
+        <v>1892</v>
+      </c>
+      <c r="C38" s="3">
+        <v>39565</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39">
+        <f t="shared" si="7"/>
+        <v>1893</v>
+      </c>
+      <c r="C39" s="3">
+        <v>43392</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40">
+        <f t="shared" si="7"/>
+        <v>1894</v>
+      </c>
+      <c r="C40" s="3">
+        <v>31758</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41">
+        <f t="shared" si="7"/>
+        <v>1895</v>
+      </c>
+      <c r="C41" s="3">
+        <v>24900</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42">
+        <f t="shared" si="7"/>
+        <v>1896</v>
+      </c>
+      <c r="C42" s="3">
+        <v>38358</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43">
+        <f t="shared" si="7"/>
+        <v>1897</v>
+      </c>
+      <c r="C43" s="3">
+        <v>25014</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44">
+        <f t="shared" si="7"/>
+        <v>1898</v>
+      </c>
+      <c r="C44" s="3">
+        <v>31196</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46">
+        <v>1882</v>
+      </c>
+      <c r="C46" s="3">
+        <v>6301</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47">
+        <v>1883</v>
+      </c>
+      <c r="C47" s="3">
+        <v>6301</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U13">
+    <sortCondition ref="A3:A13"/>
+  </sortState>
+  <mergeCells count="4">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="M1:U1"/>
+    <mergeCell ref="W1:AG1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67646A38-B248-4539-94D0-AD38AC1B418E}">
+  <dimension ref="A1:N35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="20.20703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.47265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.47265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="29">
+        <v>25.57815645334956</v>
+      </c>
+      <c r="D2" s="29">
+        <v>21</v>
+      </c>
+      <c r="E2" s="29">
+        <f>100-D2</f>
+        <v>79</v>
+      </c>
+      <c r="F2" s="33">
+        <f>C2*E2/100</f>
+        <v>20.206743598146151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="29">
+        <v>1.7730911474181921</v>
+      </c>
+      <c r="D3" s="29">
+        <v>4.8</v>
+      </c>
+      <c r="E3" s="29">
+        <f t="shared" ref="E3:E12" si="0">100-D3</f>
+        <v>95.2</v>
+      </c>
+      <c r="F3" s="33">
+        <f t="shared" ref="F3:F12" si="1">C3*E3/100</f>
+        <v>1.687982772342119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="29">
+        <v>7.5511446093347683</v>
+      </c>
+      <c r="D4" s="29">
+        <v>22.8</v>
+      </c>
+      <c r="E4" s="29">
+        <f t="shared" si="0"/>
+        <v>77.2</v>
+      </c>
+      <c r="F4" s="33">
+        <f t="shared" si="1"/>
+        <v>5.8294836384064412</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29">
+        <v>60</v>
+      </c>
+      <c r="E5" s="29">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="F5" s="33"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29">
+        <v>21.3</v>
+      </c>
+      <c r="E6" s="29">
+        <f t="shared" si="0"/>
+        <v>78.7</v>
+      </c>
+      <c r="F6" s="33"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="29">
+        <v>8.192500351107157E-2</v>
+      </c>
+      <c r="D7" s="29">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E7" s="29">
+        <f t="shared" si="0"/>
+        <v>91.3</v>
+      </c>
+      <c r="F7" s="33">
+        <f t="shared" si="1"/>
+        <v>7.4797528205608338E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="29">
+        <v>2.1019615186554939</v>
+      </c>
+      <c r="D8" s="29">
+        <v>17.5</v>
+      </c>
+      <c r="E8" s="29">
+        <f t="shared" si="0"/>
+        <v>82.5</v>
+      </c>
+      <c r="F8" s="33">
+        <f t="shared" si="1"/>
+        <v>1.7341182528907826</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29">
+        <v>26.8</v>
+      </c>
+      <c r="E9" s="29">
+        <f t="shared" si="0"/>
+        <v>73.2</v>
+      </c>
+      <c r="F9" s="33"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="29">
+        <v>24.888816066663548</v>
+      </c>
+      <c r="D10" s="29">
+        <v>21.3</v>
+      </c>
+      <c r="E10" s="29">
+        <f t="shared" si="0"/>
+        <v>78.7</v>
+      </c>
+      <c r="F10" s="33">
+        <f t="shared" si="1"/>
+        <v>19.587498244464214</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="29">
+        <v>37.939469125977247</v>
+      </c>
+      <c r="D11" s="29">
+        <v>22.7</v>
+      </c>
+      <c r="E11" s="29">
+        <f t="shared" si="0"/>
+        <v>77.3</v>
+      </c>
+      <c r="F11" s="33">
+        <f t="shared" si="1"/>
+        <v>29.327209634380409</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="29">
+        <v>5.6177145264734794E-2</v>
+      </c>
+      <c r="D12" s="29">
+        <v>25.6</v>
+      </c>
+      <c r="E12" s="29">
+        <f t="shared" si="0"/>
+        <v>74.400000000000006</v>
+      </c>
+      <c r="F12" s="33">
+        <f t="shared" si="1"/>
+        <v>4.1795796076962689E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="F13" s="33"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="33">
+        <f>SUM(F2:F12)</f>
+        <v>78.489629464912696</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>167</v>
+      </c>
+      <c r="B20" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>168</v>
+      </c>
+      <c r="B21" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>170</v>
+      </c>
+      <c r="B22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="29"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="12:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="12:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="12:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
